--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5F6D0A-A0F7-4CD8-A0C6-EE95E187CE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A6E7E6-B5B6-45EF-B544-8A1BCF5BE191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17625" yWindow="2925" windowWidth="28800" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23865" yWindow="2955" windowWidth="28800" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Food Poisoning</t>
   </si>
@@ -79,13 +79,19 @@
   </si>
   <si>
     <t xml:space="preserve">Treatment: Anti-diarrheal, electrolytes, IVCiprofloxacin AntiviralCapsules </t>
+  </si>
+  <si>
+    <t>Working</t>
+  </si>
+  <si>
+    <t>бахнуть бы 75% сразу</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,12 +101,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -131,11 +131,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -151,6 +150,143 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>81591</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>348866</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF95CB24-D584-4647-8C85-3DA0AEFD4367}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6034716" y="238126"/>
+          <a:ext cx="2705675" cy="2057400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>509246</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>298351</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A35186BE-59FC-7C05-9C73-F2FD4763CBC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8900771" y="247650"/>
+          <a:ext cx="1617905" cy="1971675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>604615</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AC14AA0-9D90-293C-6DA3-B6DE8981C1B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10658475" y="228600"/>
+          <a:ext cx="1385665" cy="2095500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,103 +552,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:B22"/>
+  <dimension ref="B3:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
-        <v>17</v>
+      <c r="C16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A6E7E6-B5B6-45EF-B544-8A1BCF5BE191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698621A3-A859-4151-AF06-F6E22ACCFEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23865" yWindow="2955" windowWidth="28800" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23865" yWindow="2955" windowWidth="28800" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Food Related (Not Done)" sheetId="1" r:id="rId1"/>
+    <sheet name="Corpse sickness" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Food Poisoning</t>
   </si>
@@ -75,26 +76,72 @@
     <t>- Prevention: Always cook wild game thoroughly!</t>
   </si>
   <si>
-    <t>- Treatment: Antiparasitic pills, albendazole injection</t>
-  </si>
-  <si>
     <t xml:space="preserve">Treatment: Anti-diarrheal, electrolytes, IVCiprofloxacin AntiviralCapsules </t>
   </si>
   <si>
     <t>Working</t>
   </si>
   <si>
-    <t>бахнуть бы 75% сразу</t>
+    <t>Treatment: Muscle relaxants, Antiparasitic pills, albendazole injection</t>
+  </si>
+  <si>
+    <t>working</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dizziness effect </t>
+  </si>
+  <si>
+    <t>Dizziness effect</t>
+  </si>
+  <si>
+    <t>LETHAL</t>
+  </si>
+  <si>
+    <t>Corpse Sickness (Putrefaction)</t>
+  </si>
+  <si>
+    <t>- Cause: Prolonged exposure to corpses in enclosed spaces (gas buildup)</t>
+  </si>
+  <si>
+    <t>- Symptoms: Eye irritation, nausea, dizziness, collapse at high exposure</t>
+  </si>
+  <si>
+    <t>- Prevention: Ventilate areas with corpses, wear gas mask or bandana</t>
+  </si>
+  <si>
+    <t>- Treatment: Get fresh air immediately</t>
+  </si>
+  <si>
+    <t>Cadaveric Aspergillosis</t>
+  </si>
+  <si>
+    <t>- Cause: Fungal spores from decomposing corpses in damp/cold environments</t>
+  </si>
+  <si>
+    <t>- Symptoms: Respiratory issues, fever, coughing</t>
+  </si>
+  <si>
+    <t>- Prevention: Wear face protection near corpses, avoid damp corpse-filled areas</t>
+  </si>
+  <si>
+    <t>- Treatment: Antifungal medication</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -109,6 +156,12 @@
       <color rgb="FF00B050"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,10 +184,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -278,6 +333,314 @@
         <a:xfrm>
           <a:off x="10658475" y="228600"/>
           <a:ext cx="1385665" cy="2095500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>191969</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A512216-F2BB-66E2-BA45-BD542E125836}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7077075" y="6124575"/>
+          <a:ext cx="1506419" cy="2190750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>523876</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>197840</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>123826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A903454D-FFC4-160E-167D-66FA7FFEED8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8915401" y="7667626"/>
+          <a:ext cx="2112364" cy="2171700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>139950</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7991404-2471-2A4E-AEA7-823877D72BD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5953126" y="3048001"/>
+          <a:ext cx="1968749" cy="3571874"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>217089</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D316A490-6C6C-7809-6C86-6B288F7B0A9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8372475" y="3048001"/>
+          <a:ext cx="2064939" cy="2343149"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>99790</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4C02166-128D-400D-8631-392EEC91D823}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10763250" y="3057525"/>
+          <a:ext cx="1385665" cy="2095500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>237497</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1EE483E-3DA5-4E3A-DFC5-340E4491EC80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12420600" y="2971800"/>
+          <a:ext cx="1694822" cy="2190750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>115491</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A29968F-ECB8-05FB-DB81-37B196F71C1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11439525" y="7620001"/>
+          <a:ext cx="1944291" cy="3505200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -552,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:C28"/>
+  <dimension ref="B3:M60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="71" customWidth="1"/>
@@ -563,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -621,41 +984,119 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>16</v>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M60" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3715F01A-79F6-4956-8F11-0E2F67879F36}">
+  <dimension ref="B3:B27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698621A3-A859-4151-AF06-F6E22ACCFEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BD5998-BBFB-4EAF-9033-2A57D84589AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23865" yWindow="2955" windowWidth="28800" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (Not Done)" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Food Poisoning</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Trichinosis</t>
   </si>
   <si>
-    <t>- Cause: Raw or undercooked wild game meat (rats, boar, bear, fox, raccoon)</t>
-  </si>
-  <si>
     <t>- Symptoms: Intense muscle pain, fever, weakness - can be LETHAL</t>
   </si>
   <si>
@@ -125,13 +122,61 @@
   </si>
   <si>
     <t>- Treatment: Antifungal medication</t>
+  </si>
+  <si>
+    <t>Mushroom/Berries Poisoning</t>
+  </si>
+  <si>
+    <t>Symptoms: Bitter taste, nausea, vomiting, dizziness, thirst/dehydration, fatigue, endurance drain. Poisonous mushrooms can damage HP and can be LETHAL if untreated</t>
+  </si>
+  <si>
+    <t>Duration: Berries 1-2 days with 1-2 hour incubation. Mushrooms 3-5 days with 2-5 hour incubation</t>
+  </si>
+  <si>
+    <t>Prevention: Do not eat unidentified wild berries/mushrooms; use Herbalist knowledge/magazines before eating foraged food</t>
+  </si>
+  <si>
+    <t>Treatment: Activated charcoal cures in ~12 hours. Anti-nausea tablets and electrolytes reduce symptoms but do not fully cure</t>
+  </si>
+  <si>
+    <r>
+      <t>Cause: Poisonous mushrooms or berries (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PoisonPower &gt; 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Mushrooms LETHATL</t>
+  </si>
+  <si>
+    <t>Cause: Raw or undercooked wild game meat (rats, boar, bear, fox, raccoon)</t>
+  </si>
+  <si>
+    <t>добавить описание в charcoal</t>
+  </si>
+  <si>
+    <t>draw зараженную кровь</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +208,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -184,12 +239,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:M60"/>
+  <dimension ref="B3:M67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="71" customWidth="1"/>
@@ -926,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -959,7 +1017,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
@@ -984,17 +1042,17 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D36" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
@@ -1004,32 +1062,68 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="13:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="M60" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B64" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B65" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B66" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B67" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1040,60 +1134,65 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3715F01A-79F6-4956-8F11-0E2F67879F36}">
-  <dimension ref="B3:B27"/>
+  <dimension ref="B3:M27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BD5998-BBFB-4EAF-9033-2A57D84589AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413A591E-1F99-46D3-8637-A20B5C57ECB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Food Related (Not Done)" sheetId="1" r:id="rId1"/>
+    <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
     <sheet name="Corpse sickness" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -26,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>Food Poisoning</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -88,9 +85,6 @@
     <t xml:space="preserve">Dizziness effect </t>
   </si>
   <si>
-    <t>Dizziness effect</t>
-  </si>
-  <si>
     <t>LETHAL</t>
   </si>
   <si>
@@ -98,9 +92,6 @@
   </si>
   <si>
     <t>- Cause: Prolonged exposure to corpses in enclosed spaces (gas buildup)</t>
-  </si>
-  <si>
-    <t>- Symptoms: Eye irritation, nausea, dizziness, collapse at high exposure</t>
   </si>
   <si>
     <t>- Prevention: Ventilate areas with corpses, wear gas mask or bandana</t>
@@ -166,10 +157,37 @@
     <t>Cause: Raw or undercooked wild game meat (rats, boar, bear, fox, raccoon)</t>
   </si>
   <si>
-    <t>добавить описание в charcoal</t>
-  </si>
-  <si>
     <t>draw зараженную кровь</t>
+  </si>
+  <si>
+    <t>Respiratory Support Kit</t>
+  </si>
+  <si>
+    <t>Corticosteroid Injection</t>
+  </si>
+  <si>
+    <t>Bronchodilator Inhaler</t>
+  </si>
+  <si>
+    <t>Anti-Nausea Tablets</t>
+  </si>
+  <si>
+    <t>Chelation Kit</t>
+  </si>
+  <si>
+    <t>CUT</t>
+  </si>
+  <si>
+    <t>heal</t>
+  </si>
+  <si>
+    <t>lowers</t>
+  </si>
+  <si>
+    <t>Symptoms: Eye irritation, nausea, dizziness, collapse at stage 3</t>
+  </si>
+  <si>
+    <t>Food Poisoning 35%++</t>
   </si>
 </sst>
 </file>
@@ -204,17 +222,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -239,15 +257,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -981,149 +1000,144 @@
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D36" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="M60" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="M60" s="3"/>
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B63" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B64" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B65" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B66" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C63" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="64" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="5" t="s">
+    <row r="67" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B67" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="D64" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="33" x14ac:dyDescent="0.25">
-      <c r="B65" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" ht="33" x14ac:dyDescent="0.25">
-      <c r="B66" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" ht="33" x14ac:dyDescent="0.25">
-      <c r="B67" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1139,60 +1153,96 @@
   <sheetData>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
+      <c r="B8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
       <c r="M9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
         <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413A591E-1F99-46D3-8637-A20B5C57ECB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A1F7F5-3AA1-4D74-9982-1A77A75AEEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -184,10 +184,138 @@
     <t>lowers</t>
   </si>
   <si>
-    <t>Symptoms: Eye irritation, nausea, dizziness, collapse at stage 3</t>
-  </si>
-  <si>
     <t>Food Poisoning 35%++</t>
+  </si>
+  <si>
+    <t>Растет от разлагающихся/гнилых трупов в сырости/холоде: дождь снаружи, мокрый персонаж, холодная температура.</t>
+  </si>
+  <si>
+    <t>Свежие трупы почти не считаются.</t>
+  </si>
+  <si>
+    <t>Помещения/улица учитываются через уже починенную corpse scan-логику, так что трупы снаружи не должны травить внутри.</t>
+  </si>
+  <si>
+    <t>Полные маски/респираторы с фильтрами блокируют, слабая защита снижает риск.</t>
+  </si>
+  <si>
+    <t>Лечение:</t>
+  </si>
+  <si>
+    <r>
+      <t>Триггерится отдельно от обычного </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>corpse_sickness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cough Syrup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Cough Suppressant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> — глушат кашель/симптомы.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bronchodilator Inhaler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> — облегчает дыхание/endurance.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Antifungal Tablets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> — реально лечат, курс около 5 дней, 10 доз по 12 часов.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>IV Amphotericin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> — быстрое лечение за 24 часа, одно применение через IV Kit, но с жесткими побочками.</t>
+    </r>
+  </si>
+  <si>
+    <t>Symptoms: Eye irritation, nausea, dizziness, fall at stage 3</t>
+  </si>
+  <si>
+    <t>corticosteroid injection добавить что лечит corpse sick</t>
+  </si>
+  <si>
+    <t>почему затригерлся corpse sickness вообще?</t>
+  </si>
+  <si>
+    <t>На 3 фазе что-то слишком сильно тратится вода</t>
+  </si>
+  <si>
+    <t>добавить заражение knox??</t>
+  </si>
+  <si>
+    <t>Kidney Stress побочка</t>
+  </si>
+  <si>
+    <t>Температура</t>
+  </si>
+  <si>
+    <t>Симптомы: жажда на 3 стадии кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
+  </si>
+  <si>
+    <t>на второй стадии слишком агрессивный fatigue</t>
   </si>
 </sst>
 </file>
@@ -257,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -267,6 +395,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1000,7 +1137,7 @@
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1148,35 +1285,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3715F01A-79F6-4956-8F11-0E2F67879F36}">
-  <dimension ref="B3:M27"/>
+  <dimension ref="B3:U39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>38</v>
       </c>
@@ -1184,7 +1321,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>39</v>
       </c>
@@ -1195,7 +1332,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>40</v>
       </c>
@@ -1203,7 +1340,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>41</v>
       </c>
@@ -1211,7 +1348,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>42</v>
       </c>
@@ -1220,29 +1357,111 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="U26" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B36" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="U36" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="U38" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A1F7F5-3AA1-4D74-9982-1A77A75AEEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFC1922-8D38-47AA-A367-0A9B24E3AAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
     <sheet name="Corpse sickness" sheetId="2" r:id="rId2"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -199,6 +200,9 @@
     <t>Полные маски/респираторы с фильтрами блокируют, слабая защита снижает риск.</t>
   </si>
   <si>
+    <t>Симптомы: кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
+  </si>
+  <si>
     <t>Лечение:</t>
   </si>
   <si>
@@ -306,16 +310,431 @@
     <t>добавить заражение knox??</t>
   </si>
   <si>
-    <t>Kidney Stress побочка</t>
-  </si>
-  <si>
-    <t>Температура</t>
-  </si>
-  <si>
-    <t>Симптомы: жажда на 3 стадии кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
-  </si>
-  <si>
-    <t>на второй стадии слишком агрессивный fatigue</t>
+    <t>жаропонижающие</t>
+  </si>
+  <si>
+    <t>Чек второго лечащего препарата</t>
+  </si>
+  <si>
+    <t>не topical;</t>
+  </si>
+  <si>
+    <t>ты принимаешь следующую дозу раньше таймера.</t>
+  </si>
+  <si>
+    <t>Сам передоз:</t>
+  </si>
+  <si>
+    <t>доза все равно засчитывается;</t>
+  </si>
+  <si>
+    <t>персонаж говорит фразу;</t>
+  </si>
+  <si>
+    <t>чем раньше выпил, тем выше intensity;</t>
+  </si>
+  <si>
+    <t>Эффекты примерно такие:</t>
+  </si>
+  <si>
+    <r>
+      <t>По текущему коду передоз не привязан напрямую к </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>tier 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Он срабатывает, если препарат:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>имеет курс </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>6+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> доз;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>имеет интервал между дозами больше </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>То есть большинство </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>tier 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> не ловят передоз, потому что они одноразовые: IV, инъекции, emergency kit, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>doseInterval = 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>dosesRequired = 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Исключение среди tier 3 сейчас: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>RifampicinComboPack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> - там </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>24h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>14 доз</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, значит ранний прием может дать передоз. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>RespiratorySupportKit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> не должен давать передоз, потому что там всего </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> дозы.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>вешается </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>medication_overdose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> на </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>8-10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> часов;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>если уже есть передоз и бахнуть еще раз, intensity усиливается до капа </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SICKNESS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> до </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>46-54%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FOOD_SICKNESS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> до </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>46-50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>THIRST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> до </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>68-76%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ENDURANCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> капается до </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>53-45%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>HP режется примерно до </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>63/56/49</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> в зависимости от intensity.</t>
+    </r>
+  </si>
+  <si>
+    <t>PEREDOS</t>
+  </si>
+  <si>
+    <t>(ПЕРЕЧЕКАТЬ ВСЕ)</t>
+  </si>
+  <si>
+    <t>добавить fever для других болезней</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3715F01A-79F6-4956-8F11-0E2F67879F36}">
-  <dimension ref="B3:U39"/>
+  <dimension ref="B3:U40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
@@ -1300,7 +1719,7 @@
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
@@ -1359,17 +1778,17 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
@@ -1392,7 +1811,7 @@
         <v>27</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
@@ -1402,7 +1821,7 @@
     </row>
     <row r="29" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
@@ -1424,44 +1843,157 @@
       <c r="B33" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="U33" s="3"/>
     </row>
     <row r="34" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B35" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="U35" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>63</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="U36" s="3"/>
     </row>
     <row r="37" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="U38" s="3"/>
     </row>
     <row r="39" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U39" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U40" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
+  <dimension ref="B3:C21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFC1922-8D38-47AA-A367-0A9B24E3AAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDBC378-BDA8-4211-845E-C328BDD1FCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
-    <sheet name="Corpse sickness" sheetId="2" r:id="rId2"/>
-    <sheet name="Mechanics" sheetId="3" r:id="rId3"/>
+    <sheet name="Corpse sickness (IGDnewMechanic" sheetId="2" r:id="rId2"/>
+    <sheet name="Wound" sheetId="4" r:id="rId3"/>
+    <sheet name="Не забыть" sheetId="5" r:id="rId4"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="89">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -200,9 +202,6 @@
     <t>Полные маски/респираторы с фильтрами блокируют, слабая защита снижает риск.</t>
   </si>
   <si>
-    <t>Симптомы: кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
-  </si>
-  <si>
     <t>Лечение:</t>
   </si>
   <si>
@@ -298,21 +297,9 @@
     <t>Symptoms: Eye irritation, nausea, dizziness, fall at stage 3</t>
   </si>
   <si>
-    <t>corticosteroid injection добавить что лечит corpse sick</t>
-  </si>
-  <si>
-    <t>почему затригерлся corpse sickness вообще?</t>
-  </si>
-  <si>
-    <t>На 3 фазе что-то слишком сильно тратится вода</t>
-  </si>
-  <si>
     <t>добавить заражение knox??</t>
   </si>
   <si>
-    <t>жаропонижающие</t>
-  </si>
-  <si>
     <t>Чек второго лечащего препарата</t>
   </si>
   <si>
@@ -735,13 +722,47 @@
   </si>
   <si>
     <t>добавить fever для других болезней</t>
+  </si>
+  <si>
+    <r>
+      <t>Antipyretic Tablets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 12 доз в упаковке, OTC tier 1, действует 4 игровых часа, снижает именно болезнь-ассоциированный fever и не должен охлаждать обычный перегрев/жару от окружения.</t>
+    </r>
+  </si>
+  <si>
+    <t>Симптомы: жажда на 2 стадии, кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
+  </si>
+  <si>
+    <t>новые бандажи (упаковка), медицинский спирт</t>
+  </si>
+  <si>
+    <t>применение для cold pack/новый итем который тает</t>
+  </si>
+  <si>
+    <t>Применение для cotton balls/затыкать кровотечение (пак)</t>
+  </si>
+  <si>
+    <t>Кашель в платок?</t>
+  </si>
+  <si>
+    <t>2 сиропа от кашля</t>
+  </si>
+  <si>
+    <t>Переделать teatonus antitoxin чтобы использовал шприц</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -783,6 +804,11 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -804,7 +830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -823,6 +849,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1704,35 +1731,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3715F01A-79F6-4956-8F11-0E2F67879F36}">
-  <dimension ref="B3:U40"/>
+  <dimension ref="B3:U42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>38</v>
       </c>
@@ -1740,18 +1767,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E9" t="s">
         <v>44</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>40</v>
       </c>
@@ -1759,7 +1786,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>41</v>
       </c>
@@ -1767,7 +1794,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>42</v>
       </c>
@@ -1776,21 +1803,6 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="O13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="O14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="O15" t="s">
-        <v>61</v>
-      </c>
-    </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>24</v>
@@ -1811,7 +1823,7 @@
         <v>27</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
@@ -1821,7 +1833,7 @@
     </row>
     <row r="29" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
@@ -1847,45 +1859,51 @@
     </row>
     <row r="34" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B35" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U35" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U36" s="3"/>
     </row>
     <row r="37" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U38" s="3"/>
     </row>
     <row r="39" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U39" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="U40" s="3" t="s">
-        <v>63</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B40" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="U42" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1894,106 +1912,151 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6996DA97-E6EC-4DC7-A46D-12151026CD00}">
+  <dimension ref="C5:M17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="5" spans="3:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="C5" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
+  <dimension ref="H10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="10" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
   <dimension ref="B3:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDBC378-BDA8-4211-845E-C328BDD1FCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9AC4AA-C060-4B32-A7AB-A3FF61CED752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -755,7 +755,52 @@
     <t>2 сиропа от кашля</t>
   </si>
   <si>
-    <t>Переделать teatonus antitoxin чтобы использовал шприц</t>
+    <t xml:space="preserve">Drag influenced fever </t>
+  </si>
+  <si>
+    <t>Новый перк: хирург</t>
+  </si>
+  <si>
+    <t>сделать реальный флаер с картинками</t>
+  </si>
+  <si>
+    <t>новый перк: не может поднять медицину выше 1, не получает знания с журнала</t>
+  </si>
+  <si>
+    <t>Минимальное разрешение окна</t>
+  </si>
+  <si>
+    <t>headache</t>
+  </si>
+  <si>
+    <t>возможно добавить механику диареи (интеграция с модом lifstyle)</t>
+  </si>
+  <si>
+    <t>добавить стресс болезнь</t>
+  </si>
+  <si>
+    <t>добавить депресуху болезнь</t>
+  </si>
+  <si>
+    <t>add immunity system later</t>
+  </si>
+  <si>
+    <t>Дистрибуция крови, добавить anti dizziness препарат, баланс длительности болезней, broken legs, проверить каждую еду на food poison, антидепресант механика которая убирает накопление депрессии на неделю-две, перевести все болезни на мудл фреймворк?, radio frequency, добавить остаточное кровотечение снижающееся со временем, убрать флаг с грибного тубика, новый UI с иконками по красивому, посмотреть на темперапуру при тричиносисе, проверить водителя которого укачивает, переделать механику severity, добавить какие-то бустеры на подобии caffeine pills, крафт лекарств, проверить препараты на побочки без болени, поддержка drug mod (выпилить скорее всего), новые бандажи (упаковка), медицинский спирт</t>
+  </si>
+  <si>
+    <t>прочекать еще раз все 3 фуд болезни</t>
+  </si>
+  <si>
+    <t>проверить все сырое мясо на работоспособность РЫБА</t>
+  </si>
+  <si>
+    <t>добавить в сендбокс опции по отключениям болезней</t>
+  </si>
+  <si>
+    <t>diziness to CAR</t>
+  </si>
+  <si>
+    <t>Alchoholic Intoxication</t>
   </si>
 </sst>
 </file>
@@ -830,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -850,6 +895,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1312,6 +1360,55 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>29479</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>162521</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FCA23F4-7683-2C80-A33A-734BF96A886E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8181975" y="171450"/>
+          <a:ext cx="6477904" cy="4267796"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1943,16 +2040,95 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="H10"/>
+  <dimension ref="C3:H31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="10" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H10" t="s">
+    <row r="3" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="H10" s="3" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C20" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C21" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C22" s="11"/>
+    </row>
+    <row r="23" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C23" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C24" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C25" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C26" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C27" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C29" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C31" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9AC4AA-C060-4B32-A7AB-A3FF61CED752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FC2037-AA33-4841-9E02-0F51FCDE8F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -801,6 +801,27 @@
   </si>
   <si>
     <t>Alchoholic Intoxication</t>
+  </si>
+  <si>
+    <t>Добавить иконки под overview/Active Medication/SideEffects</t>
+  </si>
+  <si>
+    <t>Добавить в карточку болезни симптомы если навык или книжка есть</t>
+  </si>
+  <si>
+    <t>проверить чтобы все лечащие препараты заметно снижали симптомы</t>
+  </si>
+  <si>
+    <t>TB antibiotics no active in UI</t>
+  </si>
+  <si>
+    <t>Corpse exposure</t>
+  </si>
+  <si>
+    <t>Compact mode</t>
+  </si>
+  <si>
+    <t>Добавить опыт на использование препаратов</t>
   </si>
 </sst>
 </file>
@@ -2040,35 +2061,59 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="C3:H31"/>
+  <dimension ref="C2:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="G3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="7:8" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" s="3"/>
       <c r="G4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="H10" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
         <v>91</v>
       </c>
@@ -2126,9 +2171,20 @@
         <v>103</v>
       </c>
     </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="I36" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FC2037-AA33-4841-9E02-0F51FCDE8F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553B0769-42A5-4EB3-B411-68BE12CE8BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -822,6 +822,18 @@
   </si>
   <si>
     <t>Добавить опыт на использование препаратов</t>
+  </si>
+  <si>
+    <t>Укус насекомого?</t>
+  </si>
+  <si>
+    <t>добавить все мед журналы на каждую болезнь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check doctor skill </t>
+  </si>
+  <si>
+    <t>Cadaveric Trigger Check</t>
   </si>
 </sst>
 </file>
@@ -2061,15 +2073,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="C2:I36"/>
+  <dimension ref="B2:M36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>108</v>
       </c>
@@ -2077,45 +2089,58 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3"/>
       <c r="G4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>111</v>
+      </c>
       <c r="G9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H10" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="3:7" x14ac:dyDescent="0.25">
@@ -2171,12 +2196,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="M34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="3:13" x14ac:dyDescent="0.25">
       <c r="I36" t="s">
         <v>110</v>
       </c>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553B0769-42A5-4EB3-B411-68BE12CE8BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A97133-5EFA-48EB-B1B1-F31A5FDB51DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26415" yWindow="3750" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
     <sheet name="Corpse sickness (IGDnewMechanic" sheetId="2" r:id="rId2"/>
-    <sheet name="Wound" sheetId="4" r:id="rId3"/>
+    <sheet name="Wound Infections" sheetId="6" r:id="rId3"/>
     <sheet name="Не забыть" sheetId="5" r:id="rId4"/>
     <sheet name="Mechanics" sheetId="3" r:id="rId5"/>
   </sheets>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="142">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -740,9 +740,6 @@
     <t>Симптомы: жажда на 2 стадии, кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
   </si>
   <si>
-    <t>новые бандажи (упаковка), медицинский спирт</t>
-  </si>
-  <si>
     <t>применение для cold pack/новый итем который тает</t>
   </si>
   <si>
@@ -752,9 +749,6 @@
     <t>Кашель в платок?</t>
   </si>
   <si>
-    <t>2 сиропа от кашля</t>
-  </si>
-  <si>
     <t xml:space="preserve">Drag influenced fever </t>
   </si>
   <si>
@@ -834,13 +828,100 @@
   </si>
   <si>
     <t>Cadaveric Trigger Check</t>
+  </si>
+  <si>
+    <t>Заменить /добавить нормальные painkillers</t>
+  </si>
+  <si>
+    <t>есть баг, что если начать новую игру при смерти, то перс на экран будет голый</t>
+  </si>
+  <si>
+    <t>а так же overall health status в ванильной менюшке пишет Deceased</t>
+  </si>
+  <si>
+    <t>в общем все менюки без данных</t>
+  </si>
+  <si>
+    <t>Wound Infection</t>
+  </si>
+  <si>
+    <t>nothing</t>
+  </si>
+  <si>
+    <t>pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pain, fever (38) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sepsis trigger, increased pain, fever </t>
+  </si>
+  <si>
+    <t>Cure:</t>
+  </si>
+  <si>
+    <t>Relieve</t>
+  </si>
+  <si>
+    <t>Anti-Inflammatory, anyipyretic</t>
+  </si>
+  <si>
+    <t>Сделать так, чтобы в BODY status писались все статусы при выборе части тела</t>
+  </si>
+  <si>
+    <t>Antibiotic Ointment, Broad Spectrum, IV antibiotics</t>
+  </si>
+  <si>
+    <t>Чек всех препаратов</t>
+  </si>
+  <si>
+    <t>Если нажать на иконку сердца появляется старая панель + старый HER монитор</t>
+  </si>
+  <si>
+    <t>р</t>
+  </si>
+  <si>
+    <t>Чек новый овердоз</t>
+  </si>
+  <si>
+    <t>Возможно добавить в журнал описание овердоза препаратами</t>
+  </si>
+  <si>
+    <t>Можно добавить звук на применение препаратов</t>
+  </si>
+  <si>
+    <t>И анимации</t>
+  </si>
+  <si>
+    <t>Sepsis</t>
+  </si>
+  <si>
+    <t>Cure</t>
+  </si>
+  <si>
+    <t>IV Antibiotics, Metronizadole, vancomycin, emergency sepsis kit</t>
+  </si>
+  <si>
+    <t>Fever (38) hp 85%</t>
+  </si>
+  <si>
+    <t>Fever (38.6, fatigue 50, hp 65, stress sometimes</t>
+  </si>
+  <si>
+    <t>Fever 39.4 fatigue 70, hp 30</t>
+  </si>
+  <si>
+    <t>Fever 40 fatigue 80, hp death</t>
+  </si>
+  <si>
+    <t>FASDASDASD !!!!sds!!! Переделать цвета для BODY STATUS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -887,13 +968,24 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -908,7 +1000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -927,10 +1019,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2033,7 +2126,7 @@
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U42" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2042,28 +2135,125 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6996DA97-E6EC-4DC7-A46D-12151026CD00}">
-  <dimension ref="C5:M17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2517986B-6F4C-42D0-BD39-2D6A74ACE8BD}">
+  <dimension ref="B3:N24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="6" width="29.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="5" spans="3:3" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C5" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M17" t="s">
-        <v>87</v>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K10" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E11" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F16" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N18" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2073,140 +2263,193 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="B2:M36"/>
+  <dimension ref="B2:W55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3"/>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="3:7" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C20" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C21" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C22" s="10"/>
+    </row>
+    <row r="23" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C23" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C24" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C20" s="11" t="s">
+    <row r="25" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C25" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C26" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C27" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C29" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C21" s="11" t="s">
+    <row r="31" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C31" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C22" s="11"/>
-    </row>
-    <row r="23" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C23" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C24" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C25" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C26" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C27" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C29" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C31" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
       <c r="M34" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="I36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="Q40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="W42" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="43" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="F43" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="I36" t="s">
-        <v>110</v>
+    <row r="44" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="F44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="F45" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="R46" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="R50" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P54" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="16:18" x14ac:dyDescent="0.25">
+      <c r="P55" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A97133-5EFA-48EB-B1B1-F31A5FDB51DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32343C98-E9CC-4E2D-8A12-D2D47C2B669F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="161">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>Trichinosis</t>
-  </si>
-  <si>
-    <t>- Symptoms: Intense muscle pain, fever, weakness - can be LETHAL</t>
   </si>
   <si>
     <t>- Duration: 7-14 days</t>
@@ -749,9 +746,6 @@
     <t>Кашель в платок?</t>
   </si>
   <si>
-    <t xml:space="preserve">Drag influenced fever </t>
-  </si>
-  <si>
     <t>Новый перк: хирург</t>
   </si>
   <si>
@@ -809,9 +803,6 @@
     <t>TB antibiotics no active in UI</t>
   </si>
   <si>
-    <t>Corpse exposure</t>
-  </si>
-  <si>
     <t>Compact mode</t>
   </si>
   <si>
@@ -827,9 +818,6 @@
     <t xml:space="preserve">Check doctor skill </t>
   </si>
   <si>
-    <t>Cadaveric Trigger Check</t>
-  </si>
-  <si>
     <t>Заменить /добавить нормальные painkillers</t>
   </si>
   <si>
@@ -866,15 +854,9 @@
     <t>Anti-Inflammatory, anyipyretic</t>
   </si>
   <si>
-    <t>Сделать так, чтобы в BODY status писались все статусы при выборе части тела</t>
-  </si>
-  <si>
     <t>Antibiotic Ointment, Broad Spectrum, IV antibiotics</t>
   </si>
   <si>
-    <t>Чек всех препаратов</t>
-  </si>
-  <si>
     <t>Если нажать на иконку сердца появляется старая панель + старый HER монитор</t>
   </si>
   <si>
@@ -914,14 +896,107 @@
     <t>Fever 40 fatigue 80, hp death</t>
   </si>
   <si>
-    <t>FASDASDASD !!!!sds!!! Переделать цвета для BODY STATUS</t>
+    <t>Одежда не обновляется в INFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetanus </t>
+  </si>
+  <si>
+    <t>deep wound + glass in wound</t>
+  </si>
+  <si>
+    <t>neck pain, hp30%, end 70%</t>
+  </si>
+  <si>
+    <t>body pain, fever 39, fall,hp damage, edn 50%</t>
+  </si>
+  <si>
+    <t>probably death</t>
+  </si>
+  <si>
+    <t>TetanusAntitoxin, tetanus immunoglobin</t>
+  </si>
+  <si>
+    <t>cure</t>
+  </si>
+  <si>
+    <t>Muscle relaxant, intiinflammatory, antipyretic</t>
+  </si>
+  <si>
+    <t>Prescribed Painkillers addiction</t>
+  </si>
+  <si>
+    <t>reliefe</t>
+  </si>
+  <si>
+    <t>intiinflammatory, antipyretic?</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>AntiSecpit cream prevents</t>
+  </si>
+  <si>
+    <t>Antibiotic Ointment</t>
+  </si>
+  <si>
+    <t>"-'</t>
+  </si>
+  <si>
+    <t>Add boost pills, 100% fatigue later</t>
+  </si>
+  <si>
+    <t>Cancer when smoking?</t>
+  </si>
+  <si>
+    <t>Новый перк:нельзя заразить рану</t>
+  </si>
+  <si>
+    <t>Обернуть sleeping pills в тот же UI</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Bandage были в приоритете над pain</t>
+  </si>
+  <si>
+    <r>
+      <t>если EHR уже увидел infection и завел инкубацию, заживление самой поверхностной раны больше не отменяет болезнь. Отменить инкубацию должен только явный early disinfect/antiseptic путь, иначе через 12 часов она станет </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Wound Infection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bite in the eye mechanics so character can be blind</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Сделать Cellulitis в справочнике как WIP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -973,19 +1048,23 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1000,7 +1079,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1023,7 +1102,11 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1806,10 +1889,10 @@
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -1842,7 +1925,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
@@ -1867,17 +1950,17 @@
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="D36" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
@@ -1887,27 +1970,27 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.25">
@@ -1915,35 +1998,35 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" t="s">
         <v>34</v>
-      </c>
-      <c r="C63" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="64" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="2:2" ht="33" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="2:2" ht="33" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="2:2" ht="33" x14ac:dyDescent="0.25">
       <c r="B67" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1959,174 +2042,174 @@
   <sheetData>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U33" s="3"/>
     </row>
     <row r="34" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U36" s="3"/>
     </row>
     <row r="37" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U38" s="3"/>
     </row>
     <row r="39" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B40" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U40" s="3"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U42" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2136,92 +2219,202 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2517986B-6F4C-42D0-BD39-2D6A74ACE8BD}">
-  <dimension ref="B3:N24"/>
+  <dimension ref="B3:R35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="6" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>148</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E11" s="3"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="F16" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="K10" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E11" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F16" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N18" s="12" t="s">
-        <v>141</v>
-      </c>
+      <c r="N18" s="12"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
@@ -2229,7 +2422,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
@@ -2237,7 +2430,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
@@ -2245,211 +2438,301 @@
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E24" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
         <v>136</v>
       </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="13" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G4:R12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="B2:W55"/>
+  <dimension ref="B2:W65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C3" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3"/>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H10" s="3" t="s">
-        <v>86</v>
-      </c>
+      <c r="H10" s="3"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="G15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C20" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C21" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C22" s="10"/>
+    </row>
+    <row r="23" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C23" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C24" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C20" s="10" t="s">
+    <row r="25" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C25" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C26" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C27" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C29" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C21" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C22" s="10"/>
-    </row>
-    <row r="23" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C23" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C24" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C25" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C26" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C27" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C29" s="10" t="s">
+    <row r="31" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C31" s="10" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="31" spans="3:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C31" s="10" t="s">
-        <v>101</v>
+      <c r="N31" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="M34" t="s">
-        <v>112</v>
+        <v>98</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="I36" t="s">
-        <v>108</v>
+      <c r="I36" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="3:23" x14ac:dyDescent="0.25">
       <c r="Q40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="3:23" x14ac:dyDescent="0.25">
       <c r="W42" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="F43" t="s">
-        <v>114</v>
+      <c r="F43" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="F44" t="s">
-        <v>115</v>
+      <c r="F44" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="F45" t="s">
-        <v>116</v>
+      <c r="F45" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="3:23" x14ac:dyDescent="0.25">
       <c r="R46" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" spans="16:18" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="7:18" x14ac:dyDescent="0.25">
       <c r="R50" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54" spans="16:18" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="7:18" x14ac:dyDescent="0.25">
       <c r="P54" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="55" spans="16:18" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G55" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="P55" t="s">
-        <v>133</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>154</v>
+      </c>
+      <c r="O61" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O65" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2461,105 +2744,126 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
-  <dimension ref="B3:C21"/>
+  <dimension ref="B3:Z32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
+    <row r="19" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
+      <c r="U19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
+    <row r="21" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>77</v>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="X27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="V32" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32343C98-E9CC-4E2D-8A12-D2D47C2B669F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBA1C06-2C49-42E1-9E38-0D3E76DB020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
     <sheet name="Corpse sickness (IGDnewMechanic" sheetId="2" r:id="rId2"/>
     <sheet name="Wound Infections" sheetId="6" r:id="rId3"/>
-    <sheet name="Не забыть" sheetId="5" r:id="rId4"/>
-    <sheet name="Mechanics" sheetId="3" r:id="rId5"/>
+    <sheet name="Environmental " sheetId="7" r:id="rId4"/>
+    <sheet name="Не забыть" sheetId="5" r:id="rId5"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="176">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -806,9 +807,6 @@
     <t>Compact mode</t>
   </si>
   <si>
-    <t>Добавить опыт на использование препаратов</t>
-  </si>
-  <si>
     <t>Укус насекомого?</t>
   </si>
   <si>
@@ -821,15 +819,6 @@
     <t>Заменить /добавить нормальные painkillers</t>
   </si>
   <si>
-    <t>есть баг, что если начать новую игру при смерти, то перс на экран будет голый</t>
-  </si>
-  <si>
-    <t>а так же overall health status в ванильной менюшке пишет Deceased</t>
-  </si>
-  <si>
-    <t>в общем все менюки без данных</t>
-  </si>
-  <si>
     <t>Wound Infection</t>
   </si>
   <si>
@@ -857,13 +846,7 @@
     <t>Antibiotic Ointment, Broad Spectrum, IV antibiotics</t>
   </si>
   <si>
-    <t>Если нажать на иконку сердца появляется старая панель + старый HER монитор</t>
-  </si>
-  <si>
     <t>р</t>
-  </si>
-  <si>
-    <t>Чек новый овердоз</t>
   </si>
   <si>
     <t>Возможно добавить в журнал описание овердоза препаратами</t>
@@ -990,13 +973,196 @@
   </si>
   <si>
     <t>Сделать Cellulitis в справочнике как WIP</t>
+  </si>
+  <si>
+    <t>чек новый овердоз</t>
+  </si>
+  <si>
+    <t>Blood bags fresh all the time</t>
+  </si>
+  <si>
+    <t>gene therapy adds perk</t>
+  </si>
+  <si>
+    <t>Plant Remedies</t>
+  </si>
+  <si>
+    <t>Common Cold</t>
+  </si>
+  <si>
+    <t>Pneumonia</t>
+  </si>
+  <si>
+    <t>Hypothermia</t>
+  </si>
+  <si>
+    <t>Heat Exhaustion</t>
+  </si>
+  <si>
+    <t>Триггер есть через body temp выше 40.5C или fallback hot exposure. Есть жажда, судороги, dizziness, vomiting, прогрессия в Heat Stroke. Тут ядро выглядит рабочим. Но лекарства типа electrolytes/rehydration работают скорее через общий hydration support/cure timer, а не через полноценное “снять симптомы heat exhaustion”.</t>
+  </si>
+  <si>
+    <t>Heat Stroke</t>
+  </si>
+  <si>
+    <t>Появляется как прогрессия из Heat Exhaustion. Есть collapse/confusion/thirst и летальность. Главная проблема: cooling блокирует recovery, но death check не учитывает “уже охлаждаюсь/лечусь” так же явно, как hypothermia учитывает тепло. То есть риск смерти может быть слишком тупым и старомодным.</t>
+  </si>
+  <si>
+    <t>Dysentery</t>
+  </si>
+  <si>
+    <r>
+      <t>Триггер есть: холод/мокрота/экспозиция. Симптомы частично есть: чихание, диалоги, лёгкая усталость, fever на 3 стадии. Может перейти в Pneumonia. Но лечение простуды сейчас, похоже, не снижает шанс перехода в Pneumonia, потому что код смотрит старый флаг </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>disease.treated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, а новая медикамент-система его не ставит.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Появляется из Common Cold. Кашель с шумом для зомби есть, fever есть, летальность есть. Но “smoke/dust” как причина в комментариях есть, а реального триггера от дыма/пыли не нашёл. Лечение антибиотиками/стероидами должно запускать cure timer, но снижение смертельного риска тоже завязано на старый </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>disease.treated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, значит во время лечения шанс смерти может не снижаться как задумано.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Триггер через новую body temperature систему есть: опасная зона ниже 34C, плюс fallback через холод/мокроту. Выздоровление правильно требует тепло. Но симптомы самой болезни слабовато применяются: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>temperatureDrain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> и </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>staminaPenalty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> прописаны в definition, но в environmental effect handler они фактически не обрабатываются. Основное ощущение холода, вероятно, идёт из </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>EHR_BodyTemperature</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, а не из disease stage.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Триггер есть, но узкий: сейчас hook ловит </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ISDrinkFromBottle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> и tainted water. Прямые источники типа river/toilet/tap/rainCollector в коде рассчитаны, но я не вижу реального hook-а, который передаёт эти sourceType из мира. Симптомы есть: thirst/hunger drain, vomiting, blood loss. Но anti-diarrheal почти наверняка не влияет на core drain, потому что </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>diarrhea</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> reduction нигде в environmental effect handler не читается. Летальность через dehydration оставлена ванили: мод просто держит thirst на максимуме, сам HP не добивает.</t>
+    </r>
+  </si>
+  <si>
+    <t>Severe vomiting, blood loss, extreme dehydration - can be LETHAL</t>
+  </si>
+  <si>
+    <t>oral hydration сделать чтобы работал и на другие болезни</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cure: </t>
+  </si>
+  <si>
+    <t>Relieve: antiinflamation? antinausea, electolytpowder, oral hydration</t>
+  </si>
+  <si>
+    <t>Check all 4 stages</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1058,6 +1224,16 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1079,7 +1255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1102,9 +1278,23 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1975,7 +2165,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
@@ -2227,13 +2417,13 @@
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2241,276 +2431,271 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
+        <v>111</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
+        <v>112</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
+        <v>113</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
+        <v>117</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+        <v>116</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
+        <v>142</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="F16" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N18" s="12"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="F16" s="3"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D21">
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D22">
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E24" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D25" t="s">
-        <v>145</v>
-      </c>
-      <c r="E25" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>136</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D30">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D31">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>141</v>
+        <v>136</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="s">
-        <v>137</v>
+      <c r="B35" s="12" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2522,6 +2707,172 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EED2F2-04B6-485E-917E-1A8DD36BA090}">
+  <dimension ref="B3:I44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="72.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="16"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="16"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="16"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="99" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="16"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B28" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="17"/>
+    </row>
+    <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="17"/>
+    </row>
+    <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="17"/>
+    </row>
+    <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="17"/>
+    </row>
+    <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="17"/>
+    </row>
+    <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="17"/>
+    </row>
+    <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="17"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="17"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="17"/>
+    </row>
+    <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B32:B41"/>
+    <mergeCell ref="C42:H43"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
   <dimension ref="B2:W65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2560,7 +2911,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G9" t="s">
         <v>103</v>
@@ -2571,7 +2922,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
@@ -2586,10 +2937,10 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G15" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
@@ -2644,8 +2995,16 @@
       <c r="C31" s="10" t="s">
         <v>99</v>
       </c>
+      <c r="J31" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="N31" t="s">
-        <v>160</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="H33" s="3" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="3:23" x14ac:dyDescent="0.25">
@@ -2653,17 +3012,18 @@
         <v>98</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="I36" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="I36" s="3"/>
     </row>
     <row r="39" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="Q39" t="s">
         <v>82</v>
@@ -2674,65 +3034,67 @@
         <v>83</v>
       </c>
     </row>
+    <row r="41" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="K41" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
     <row r="42" spans="3:23" x14ac:dyDescent="0.25">
       <c r="W42" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="F43" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="F44" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="F45" s="3" t="s">
-        <v>112</v>
-      </c>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="R46" s="3" t="s">
-        <v>122</v>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="48" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="I48" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="7:18" x14ac:dyDescent="0.25">
       <c r="R50" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="7:18" x14ac:dyDescent="0.25">
       <c r="P54" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="7:18" x14ac:dyDescent="0.25">
       <c r="G55" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="P55" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="7:18" x14ac:dyDescent="0.25">
       <c r="G61" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="O61" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="7:18" x14ac:dyDescent="0.25">
       <c r="G62" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="15:15" x14ac:dyDescent="0.25">
       <c r="O65" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2742,7 +3104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
   <dimension ref="B3:Z32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2835,7 +3197,7 @@
         <v>74</v>
       </c>
       <c r="U19" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
@@ -2850,20 +3212,20 @@
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
       <c r="X27" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="Z27" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
       <c r="T28" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.25">
       <c r="V32" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBA1C06-2C49-42E1-9E38-0D3E76DB020D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5F1454-8FFE-44C5-A4BA-26900B7AFE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="177">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1146,9 +1146,6 @@
     <t>Severe vomiting, blood loss, extreme dehydration - can be LETHAL</t>
   </si>
   <si>
-    <t>oral hydration сделать чтобы работал и на другие болезни</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cure: </t>
   </si>
   <si>
@@ -1156,13 +1153,19 @@
   </si>
   <si>
     <t>Check all 4 stages</t>
+  </si>
+  <si>
+    <t>Lifestyle intecgration</t>
+  </si>
+  <si>
+    <t>Add medical watches</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1234,6 +1237,12 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF92D050"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1255,7 +1264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1279,9 +1288,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1291,11 +1297,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2433,20 +2445,20 @@
       <c r="E4" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2455,18 +2467,18 @@
       <c r="E5" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2475,18 +2487,18 @@
       <c r="E6" t="s">
         <v>113</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -2495,18 +2507,18 @@
       <c r="E7" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -2515,78 +2527,78 @@
       <c r="E8" t="s">
         <v>116</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>142</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -2715,90 +2727,90 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="16"/>
+      <c r="B11" s="15"/>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="16"/>
+      <c r="B12" s="15"/>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="16"/>
+      <c r="B13" s="15"/>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="16"/>
+      <c r="B14" s="15"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="16"/>
+      <c r="B20" s="15"/>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="16"/>
+      <c r="B21" s="15"/>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="16"/>
+      <c r="B22" s="15"/>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="99" x14ac:dyDescent="0.25">
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="16"/>
+      <c r="B25" s="15"/>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="16"/>
+      <c r="B26" s="15"/>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="16"/>
+      <c r="B29" s="15"/>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="16"/>
+      <c r="B30" s="15"/>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="19" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2839,18 +2851,19 @@
         <v>171</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D42" s="18"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
       <c r="G42" s="18"/>
       <c r="H42" s="18"/>
-      <c r="I42" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>175</v>
+      </c>
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
@@ -2860,7 +2873,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2996,7 +3009,7 @@
         <v>99</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N31" t="s">
         <v>154</v>
@@ -3017,6 +3030,9 @@
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I36" s="3"/>
+      <c r="L36" s="3" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="39" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D39" t="s">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5F1454-8FFE-44C5-A4BA-26900B7AFE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9E95EA-5D2F-4D5C-86B1-BF2A347437AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="182">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -990,9 +990,6 @@
     <t>Common Cold</t>
   </si>
   <si>
-    <t>Pneumonia</t>
-  </si>
-  <si>
     <t>Hypothermia</t>
   </si>
   <si>
@@ -1012,7 +1009,7 @@
   </si>
   <si>
     <r>
-      <t>Триггер есть: холод/мокрота/экспозиция. Симптомы частично есть: чихание, диалоги, лёгкая усталость, fever на 3 стадии. Может перейти в Pneumonia. Но лечение простуды сейчас, похоже, не снижает шанс перехода в Pneumonia, потому что код смотрит старый флаг </t>
+      <t>Триггер через новую body temperature систему есть: опасная зона ниже 34C, плюс fallback через холод/мокроту. Выздоровление правильно требует тепло. Но симптомы самой болезни слабовато применяются: </t>
     </r>
     <r>
       <rPr>
@@ -1020,20 +1017,15 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>disease.treated</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, а новая медикамент-система его не ставит.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Появляется из Common Cold. Кашель с шумом для зомби есть, fever есть, летальность есть. Но “smoke/dust” как причина в комментариях есть, а реального триггера от дыма/пыли не нашёл. Лечение антибиотиками/стероидами должно запускать cure timer, но снижение смертельного риска тоже завязано на старый </t>
+      <t>temperatureDrain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> и </t>
     </r>
     <r>
       <rPr>
@@ -1041,20 +1033,15 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>disease.treated</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, значит во время лечения шанс смерти может не снижаться как задумано.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Триггер через новую body temperature систему есть: опасная зона ниже 34C, плюс fallback через холод/мокроту. Выздоровление правильно требует тепло. Но симптомы самой болезни слабовато применяются: </t>
+      <t>staminaPenalty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> прописаны в definition, но в environmental effect handler они фактически не обрабатываются. Основное ощущение холода, вероятно, идёт из </t>
     </r>
     <r>
       <rPr>
@@ -1062,15 +1049,20 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>temperatureDrain</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> и </t>
+      <t>EHR_BodyTemperature</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, а не из disease stage.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Триггер есть, но узкий: сейчас hook ловит </t>
     </r>
     <r>
       <rPr>
@@ -1078,15 +1070,15 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>staminaPenalty</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> прописаны в definition, но в environmental effect handler они фактически не обрабатываются. Основное ощущение холода, вероятно, идёт из </t>
+      <t>ISDrinkFromBottle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> и tainted water. Прямые источники типа river/toilet/tap/rainCollector в коде рассчитаны, но я не вижу реального hook-а, который передаёт эти sourceType из мира. Симптомы есть: thirst/hunger drain, vomiting, blood loss. Но anti-diarrheal почти наверняка не влияет на core drain, потому что </t>
     </r>
     <r>
       <rPr>
@@ -1094,20 +1086,120 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>EHR_BodyTemperature</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, а не из disease stage.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Триггер есть, но узкий: сейчас hook ловит </t>
+      <t>diarrhea</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> reduction нигде в environmental effect handler не читается. Летальность через dehydration оставлена ванили: мод просто держит thirst на максимуме, сам HP не добивает.</t>
+    </r>
+  </si>
+  <si>
+    <t>Severe vomiting, blood loss, extreme dehydration - can be LETHAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cure: </t>
+  </si>
+  <si>
+    <t>Relieve: antiinflamation? antinausea, electolytpowder, oral hydration</t>
+  </si>
+  <si>
+    <t>Check all 4 stages</t>
+  </si>
+  <si>
+    <t>Lifestyle intecgration</t>
+  </si>
+  <si>
+    <t>Add medical watches that required to see blood level</t>
+  </si>
+  <si>
+    <t>Ванная</t>
+  </si>
+  <si>
+    <t>Стадия 1 почти без видимых эффектов, фразы/sniff.
+Стадия 2 включает ванильный cold-мудл, чихание + SFX, fatigue cap 10%, температура 37.5.
+Стадия 3 сильнее: cold-мудл, диалоги/чихание, температура 38.0, fatigue ограничен мягко до 25%.
+Стадия 4 теперь без симптомов, как recovery. Если лечения нет, сразу кидается 50% roll: либо Pneumonia, либо выздоровление. Если лечение активно, осложнение не роллится.</t>
+  </si>
+  <si>
+    <r>
+      <t>Vitamins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> / ванильные витамины: легкая поддержка, не cure.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cold &amp; Flu Tablets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: relief симптомов, fever/fatigue/pain, не cure.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Antipyretic Tablets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: снижает fever.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cough Syrup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: снижает кашель/чихание.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cough Suppressant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: снижает кашель/чихание.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Antiviral Capsules</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: уже реальное лечение, курс </t>
     </r>
     <r>
       <rPr>
@@ -1115,15 +1207,15 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>ISDrinkFromBottle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> и tainted water. Прямые источники типа river/toilet/tap/rainCollector в коде рассчитаны, но я не вижу реального hook-а, который передаёт эти sourceType из мира. Симптомы есть: thirst/hunger drain, vomiting, blood loss. Но anti-diarrheal почти наверняка не влияет на core drain, потому что </t>
+      <t>6 доз</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, каждые </t>
     </r>
     <r>
       <rPr>
@@ -1131,41 +1223,39 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>diarrhea</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> reduction нигде в environmental effect handler не читается. Летальность через dehydration оставлена ванили: мод просто держит thirst на максимуме, сам HP не добивает.</t>
-    </r>
-  </si>
-  <si>
-    <t>Severe vomiting, blood loss, extreme dehydration - can be LETHAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cure: </t>
-  </si>
-  <si>
-    <t>Relieve: antiinflamation? antinausea, electolytpowder, oral hydration</t>
-  </si>
-  <si>
-    <t>Check all 4 stages</t>
-  </si>
-  <si>
-    <t>Lifestyle intecgration</t>
-  </si>
-  <si>
-    <t>Add medical watches</t>
+      <t>8h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, cure примерно </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>48h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1243,6 +1333,27 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1264,7 +1375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1308,6 +1419,18 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2731,92 +2854,106 @@
         <v>159</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+    <row r="4" spans="2:2" ht="132" x14ac:dyDescent="0.25">
+      <c r="B4" s="21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B12" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="2:8" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="15"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="15"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="99" x14ac:dyDescent="0.25">
+      <c r="B24" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="15"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B28" s="21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="15"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="15"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="17" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="15"/>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="15"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="15"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="15"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" ht="99" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="15"/>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="15"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="14" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="15"/>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="15"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="17" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2848,10 +2985,10 @@
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D42" s="18"/>
       <c r="E42" s="18"/>
@@ -2862,7 +2999,7 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
@@ -2873,7 +3010,7 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3009,7 +3146,7 @@
         <v>99</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N31" t="s">
         <v>154</v>
@@ -3031,7 +3168,7 @@
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="3:23" x14ac:dyDescent="0.25">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9E95EA-5D2F-4D5C-86B1-BF2A347437AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3D6526-FA41-4ED3-9BFE-2B76ED893202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="188">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -738,9 +738,6 @@
     <t>Симптомы: жажда на 2 стадии, кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
   </si>
   <si>
-    <t>применение для cold pack/новый итем который тает</t>
-  </si>
-  <si>
     <t>Применение для cotton balls/затыкать кровотечение (пак)</t>
   </si>
   <si>
@@ -762,9 +759,6 @@
     <t>headache</t>
   </si>
   <si>
-    <t>возможно добавить механику диареи (интеграция с модом lifstyle)</t>
-  </si>
-  <si>
     <t>добавить стресс болезнь</t>
   </si>
   <si>
@@ -805,9 +799,6 @@
   </si>
   <si>
     <t>Compact mode</t>
-  </si>
-  <si>
-    <t>Укус насекомого?</t>
   </si>
   <si>
     <t>добавить все мед журналы на каждую болезнь</t>
@@ -1249,13 +1240,51 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>Stage 1: 38.0, лёгкий кашель через ehr_cough_male/female, chest pain лёгкий.
+Stage 2: 40.0, severe cough, endurance cap 70%, боль в груди.
+Stage 3: то же + HP drain с капом до 30% HP.
+Stage 4: то же + HP drain без капа.
+Старый random death roll для pneumonia выключен, теперь летальность идёт через понятный HP drain.
+Cough Syrup / Cough Suppressant теперь не “лечат” и не стопают HP drain, а только режут кашель.
+Bronchodilator облегчает дыхание/endurance cap.
+Antipyretic снижает fever.
+Prescription Antibiotics и Broad Spectrum Antibiotics лечат.
+IV Ciprofloxacin лечит pneumonia как быстрый clinical cure, tooltip/таймер выставлены на фактические 12h.
+Corticosteroid Injection убран из лечения pneumonia, оставлен для corpse sickness.
+Обновил справочник и EN tooltips, чтобы UI не показывал старую правду.</t>
+  </si>
+  <si>
+    <t>Pneumonia</t>
+  </si>
+  <si>
+    <t>Ванная должна лечить HeatStroke</t>
+  </si>
+  <si>
+    <t>Возможно поменять HeatExposure с 33 градусов</t>
+  </si>
+  <si>
+    <t>Укус насекомого? Если очень долго сидеть на траве</t>
+  </si>
+  <si>
+    <t>Чекнуть perk cost</t>
+  </si>
+  <si>
+    <t>Antibodies mod compability</t>
+  </si>
+  <si>
+    <t>Blood Types Compability hidden behind flyer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1349,11 +1378,6 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1408,15 +1432,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1431,6 +1446,15 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2300,7 +2324,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
@@ -2534,7 +2558,7 @@
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U42" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2552,13 +2576,13 @@
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2566,175 +2590,175 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
+        <v>109</v>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="21"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
+        <v>110</v>
+      </c>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s">
         <v>114</v>
       </c>
-      <c r="E7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
+        <v>113</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>142</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
+        <v>139</v>
+      </c>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
@@ -2742,7 +2766,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
@@ -2750,7 +2774,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
@@ -2758,34 +2782,34 @@
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
@@ -2793,7 +2817,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
@@ -2801,7 +2825,7 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
@@ -2809,28 +2833,28 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2843,7 +2867,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EED2F2-04B6-485E-917E-1A8DD36BA090}">
-  <dimension ref="B3:I44"/>
+  <dimension ref="B3:I48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="72.7109375" customWidth="1"/>
@@ -2851,58 +2875,63 @@
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" ht="132" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="20" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
+    <row r="10" spans="2:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="20" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
+    <row r="11" spans="2:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+    <row r="12" spans="2:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="20" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" ht="33" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="2:8" ht="115.5" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
@@ -2912,13 +2941,13 @@
       <c r="B22" s="15"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="20" t="s">
-        <v>161</v>
+      <c r="B23" s="17" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="99" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
@@ -2928,16 +2957,16 @@
       <c r="B26" s="15"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="20" t="s">
-        <v>163</v>
+      <c r="B27" s="17" t="s">
+        <v>160</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="21" t="s">
-        <v>164</v>
+      <c r="B28" s="18" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
@@ -2947,70 +2976,80 @@
       <c r="B30" s="15"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
-        <v>165</v>
+      <c r="B31" s="16" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="17" t="s">
-        <v>167</v>
+      <c r="B32" s="22" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="17"/>
+      <c r="B33" s="22"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="17"/>
+      <c r="B34" s="22"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="17"/>
+      <c r="B35" s="22"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="17"/>
+      <c r="B36" s="22"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="17"/>
+      <c r="B37" s="22"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="17"/>
+      <c r="B38" s="22"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="17"/>
+      <c r="B39" s="22"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="17"/>
+      <c r="B40" s="22"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="17"/>
+      <c r="B41" s="22"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
+        <v>165</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>172</v>
-      </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
+        <v>169</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>169</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="255" x14ac:dyDescent="0.25">
+      <c r="B48" s="15" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3024,230 +3063,243 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="B2:W65"/>
+  <dimension ref="A2:W65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="3"/>
       <c r="G3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3"/>
       <c r="G4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>184</v>
+      </c>
+      <c r="G9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>105</v>
-      </c>
-      <c r="G9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H10" s="3"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="G14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>107</v>
-      </c>
       <c r="G15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C21" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C22" s="10"/>
     </row>
     <row r="23" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C23" s="10" t="s">
-        <v>90</v>
-      </c>
+      <c r="C23" s="10"/>
     </row>
     <row r="24" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C24" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C25" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C26" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C27" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C29" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C31" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N31" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="3:23" x14ac:dyDescent="0.25">
       <c r="H33" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="3:23" x14ac:dyDescent="0.25">
       <c r="Q40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="3:23" x14ac:dyDescent="0.25">
       <c r="K41" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="3:23" x14ac:dyDescent="0.25">
       <c r="W42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="3:23" x14ac:dyDescent="0.25">
       <c r="F43" s="3"/>
+      <c r="K43" s="3" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="44" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="F44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="45" spans="3:23" x14ac:dyDescent="0.25">
       <c r="F45" s="3"/>
+      <c r="K45" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="46" spans="3:23" x14ac:dyDescent="0.25">
       <c r="R46" s="3"/>
     </row>
+    <row r="47" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>186</v>
+      </c>
+    </row>
     <row r="48" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I48" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="50" spans="7:18" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C49" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.25">
       <c r="R50" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" spans="7:18" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.25">
       <c r="P54" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="7:18" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G55" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="61" spans="7:18" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G61" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O61" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="62" spans="7:18" x14ac:dyDescent="0.25">
-      <c r="G62" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="65" spans="15:15" x14ac:dyDescent="0.25">
       <c r="O65" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3350,7 +3402,7 @@
         <v>74</v>
       </c>
       <c r="U19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
@@ -3365,20 +3417,20 @@
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
       <c r="X27" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="Z27" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
       <c r="T28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.25">
       <c r="V32" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3D6526-FA41-4ED3-9BFE-2B76ED893202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9912772-BD8B-4173-A730-BB2C35C97689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,9 @@
     <sheet name="Corpse sickness (IGDnewMechanic" sheetId="2" r:id="rId2"/>
     <sheet name="Wound Infections" sheetId="6" r:id="rId3"/>
     <sheet name="Environmental " sheetId="7" r:id="rId4"/>
-    <sheet name="Не забыть" sheetId="5" r:id="rId5"/>
-    <sheet name="Mechanics" sheetId="3" r:id="rId6"/>
+    <sheet name="Blood" sheetId="8" r:id="rId5"/>
+    <sheet name="Не забыть" sheetId="5" r:id="rId6"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="194">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1278,6 +1279,25 @@
   </si>
   <si>
     <t>Blood Types Compability hidden behind flyer</t>
+  </si>
+  <si>
+    <t>Добавить after bleed</t>
+  </si>
+  <si>
+    <t>только для deep wound</t>
+  </si>
+  <si>
+    <t>накопление Corpse sickness старутет сразу с 20-30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 1 (1-6 часов),дилоги, Endurance cap 30%, lower back pain. Stage 2 Endurance cap 40%, lower back pain, hp drain, hp cap 50%, диалоги, sickness (nausea). temperature 40, stage 3 все то же самое, но без капа хп, 4 стадия такая же(может новые диалоги). Иконка для болезни уже лежит в textures под именем EHR_Disease_AHTR.png
+По лечению нужно будет добавить несколько новых препаратов: IV Fluids, курс 24 часа (Item_IVFluids.png), Furosemide, курс 48 часов (.png) Side Effect - Dehydration(high thirst), lower back pain.   </t>
+  </si>
+  <si>
+    <t>influenza?</t>
+  </si>
+  <si>
+    <t>spoiled bags can be used and triggers AHTR</t>
   </si>
 </sst>
 </file>
@@ -3062,6 +3082,135 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D345CE2-5F04-48E0-AE34-8739DA490F25}">
+  <dimension ref="B3:M28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="61.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:13" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="15"/>
+    </row>
+    <row r="4" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="23"/>
+      <c r="C4" s="15"/>
+    </row>
+    <row r="5" spans="2:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="23"/>
+      <c r="C5" s="15"/>
+    </row>
+    <row r="6" spans="2:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="23"/>
+      <c r="C6" s="15"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="23"/>
+      <c r="C7" s="15"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="23"/>
+      <c r="C8" s="15"/>
+      <c r="M8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="23"/>
+      <c r="C9" s="15"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="F11" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:B9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
   <dimension ref="A2:W65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3132,53 +3281,53 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:23" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C21" s="10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C22" s="10"/>
     </row>
-    <row r="23" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C23" s="10"/>
     </row>
-    <row r="24" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C24" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C25" s="10" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C26" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C27" s="10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C29" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="3:14" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C31" s="10" t="s">
         <v>97</v>
       </c>
@@ -3187,6 +3336,11 @@
       </c>
       <c r="N31" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="W32" s="3" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="3:23" x14ac:dyDescent="0.25">
@@ -3200,6 +3354,14 @@
       </c>
       <c r="Q34" s="3" t="s">
         <v>135</v>
+      </c>
+      <c r="W34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="W35" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
@@ -3216,11 +3378,6 @@
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="Q40" t="s">
-        <v>82</v>
-      </c>
-    </row>
     <row r="41" spans="3:23" x14ac:dyDescent="0.25">
       <c r="K41" s="3" t="s">
         <v>155</v>
@@ -3232,6 +3389,9 @@
       </c>
     </row>
     <row r="43" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="C43" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="F43" s="3"/>
       <c r="K43" s="3" t="s">
         <v>182</v>
@@ -3309,7 +3469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
   <dimension ref="B3:Z32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9912772-BD8B-4173-A730-BB2C35C97689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43360C05-6C01-4B38-AFA0-27D62E734630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3120" windowWidth="28800" windowHeight="14355" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="3180" windowWidth="28800" windowHeight="14355" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="190">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -296,35 +296,225 @@
     <t>Symptoms: Eye irritation, nausea, dizziness, fall at stage 3</t>
   </si>
   <si>
-    <t>добавить заражение knox??</t>
-  </si>
-  <si>
     <t>Чек второго лечащего препарата</t>
   </si>
   <si>
-    <t>не topical;</t>
-  </si>
-  <si>
-    <t>ты принимаешь следующую дозу раньше таймера.</t>
-  </si>
-  <si>
-    <t>Сам передоз:</t>
-  </si>
-  <si>
-    <t>доза все равно засчитывается;</t>
-  </si>
-  <si>
-    <t>персонаж говорит фразу;</t>
-  </si>
-  <si>
-    <t>чем раньше выпил, тем выше intensity;</t>
-  </si>
-  <si>
-    <t>Эффекты примерно такие:</t>
-  </si>
-  <si>
-    <r>
-      <t>По текущему коду передоз не привязан напрямую к </t>
+    <t>добавить fever для других болезней</t>
+  </si>
+  <si>
+    <r>
+      <t>Antipyretic Tablets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 12 доз в упаковке, OTC tier 1, действует 4 игровых часа, снижает именно болезнь-ассоциированный fever и не должен охлаждать обычный перегрев/жару от окружения.</t>
+    </r>
+  </si>
+  <si>
+    <t>Симптомы: жажда на 2 стадии, кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
+  </si>
+  <si>
+    <t>Применение для cotton balls/затыкать кровотечение (пак)</t>
+  </si>
+  <si>
+    <t>Кашель в платок?</t>
+  </si>
+  <si>
+    <t>Новый перк: хирург</t>
+  </si>
+  <si>
+    <t>сделать реальный флаер с картинками</t>
+  </si>
+  <si>
+    <t>новый перк: не может поднять медицину выше 1, не получает знания с журнала</t>
+  </si>
+  <si>
+    <t>Минимальное разрешение окна</t>
+  </si>
+  <si>
+    <t>headache</t>
+  </si>
+  <si>
+    <t>добавить стресс болезнь</t>
+  </si>
+  <si>
+    <t>добавить депресуху болезнь</t>
+  </si>
+  <si>
+    <t>add immunity system later</t>
+  </si>
+  <si>
+    <t>Дистрибуция крови, добавить anti dizziness препарат, баланс длительности болезней, broken legs, проверить каждую еду на food poison, антидепресант механика которая убирает накопление депрессии на неделю-две, перевести все болезни на мудл фреймворк?, radio frequency, добавить остаточное кровотечение снижающееся со временем, убрать флаг с грибного тубика, новый UI с иконками по красивому, посмотреть на темперапуру при тричиносисе, проверить водителя которого укачивает, переделать механику severity, добавить какие-то бустеры на подобии caffeine pills, крафт лекарств, проверить препараты на побочки без болени, поддержка drug mod (выпилить скорее всего), новые бандажи (упаковка), медицинский спирт</t>
+  </si>
+  <si>
+    <t>прочекать еще раз все 3 фуд болезни</t>
+  </si>
+  <si>
+    <t>проверить все сырое мясо на работоспособность РЫБА</t>
+  </si>
+  <si>
+    <t>добавить в сендбокс опции по отключениям болезней</t>
+  </si>
+  <si>
+    <t>diziness to CAR</t>
+  </si>
+  <si>
+    <t>Alchoholic Intoxication</t>
+  </si>
+  <si>
+    <t>Добавить иконки под overview/Active Medication/SideEffects</t>
+  </si>
+  <si>
+    <t>Добавить в карточку болезни симптомы если навык или книжка есть</t>
+  </si>
+  <si>
+    <t>проверить чтобы все лечащие препараты заметно снижали симптомы</t>
+  </si>
+  <si>
+    <t>TB antibiotics no active in UI</t>
+  </si>
+  <si>
+    <t>Compact mode</t>
+  </si>
+  <si>
+    <t>добавить все мед журналы на каждую болезнь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check doctor skill </t>
+  </si>
+  <si>
+    <t>Заменить /добавить нормальные painkillers</t>
+  </si>
+  <si>
+    <t>Wound Infection</t>
+  </si>
+  <si>
+    <t>nothing</t>
+  </si>
+  <si>
+    <t>pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pain, fever (38) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sepsis trigger, increased pain, fever </t>
+  </si>
+  <si>
+    <t>Cure:</t>
+  </si>
+  <si>
+    <t>Relieve</t>
+  </si>
+  <si>
+    <t>Anti-Inflammatory, anyipyretic</t>
+  </si>
+  <si>
+    <t>Antibiotic Ointment, Broad Spectrum, IV antibiotics</t>
+  </si>
+  <si>
+    <t>р</t>
+  </si>
+  <si>
+    <t>Возможно добавить в журнал описание овердоза препаратами</t>
+  </si>
+  <si>
+    <t>Можно добавить звук на применение препаратов</t>
+  </si>
+  <si>
+    <t>И анимации</t>
+  </si>
+  <si>
+    <t>Sepsis</t>
+  </si>
+  <si>
+    <t>Cure</t>
+  </si>
+  <si>
+    <t>IV Antibiotics, Metronizadole, vancomycin, emergency sepsis kit</t>
+  </si>
+  <si>
+    <t>Fever (38) hp 85%</t>
+  </si>
+  <si>
+    <t>Fever (38.6, fatigue 50, hp 65, stress sometimes</t>
+  </si>
+  <si>
+    <t>Fever 39.4 fatigue 70, hp 30</t>
+  </si>
+  <si>
+    <t>Fever 40 fatigue 80, hp death</t>
+  </si>
+  <si>
+    <t>Одежда не обновляется в INFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetanus </t>
+  </si>
+  <si>
+    <t>deep wound + glass in wound</t>
+  </si>
+  <si>
+    <t>neck pain, hp30%, end 70%</t>
+  </si>
+  <si>
+    <t>body pain, fever 39, fall,hp damage, edn 50%</t>
+  </si>
+  <si>
+    <t>probably death</t>
+  </si>
+  <si>
+    <t>TetanusAntitoxin, tetanus immunoglobin</t>
+  </si>
+  <si>
+    <t>cure</t>
+  </si>
+  <si>
+    <t>Muscle relaxant, intiinflammatory, antipyretic</t>
+  </si>
+  <si>
+    <t>Prescribed Painkillers addiction</t>
+  </si>
+  <si>
+    <t>reliefe</t>
+  </si>
+  <si>
+    <t>intiinflammatory, antipyretic?</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>AntiSecpit cream prevents</t>
+  </si>
+  <si>
+    <t>Antibiotic Ointment</t>
+  </si>
+  <si>
+    <t>"-'</t>
+  </si>
+  <si>
+    <t>Cancer when smoking?</t>
+  </si>
+  <si>
+    <t>Новый перк:нельзя заразить рану</t>
+  </si>
+  <si>
+    <t>Обернуть sleeping pills в тот же UI</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Bandage были в приоритете над pain</t>
+  </si>
+  <si>
+    <r>
+      <t>если EHR уже увидел infection и завел инкубацию, заживление самой поверхностной раны больше не отменяет болезнь. Отменить инкубацию должен только явный early disinfect/antiseptic путь, иначе через 12 часов она станет </t>
     </r>
     <r>
       <rPr>
@@ -332,7 +522,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>tier 3</t>
+      <t>Wound Infection</t>
     </r>
     <r>
       <rPr>
@@ -340,12 +530,54 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>. Он срабатывает, если препарат:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>имеет курс </t>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bite in the eye mechanics so character can be blind</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Сделать Cellulitis в справочнике как WIP</t>
+  </si>
+  <si>
+    <t>чек новый овердоз</t>
+  </si>
+  <si>
+    <t>Blood bags fresh all the time</t>
+  </si>
+  <si>
+    <t>gene therapy adds perk</t>
+  </si>
+  <si>
+    <t>Plant Remedies</t>
+  </si>
+  <si>
+    <t>Common Cold</t>
+  </si>
+  <si>
+    <t>Hypothermia</t>
+  </si>
+  <si>
+    <t>Heat Exhaustion</t>
+  </si>
+  <si>
+    <t>Триггер есть через body temp выше 40.5C или fallback hot exposure. Есть жажда, судороги, dizziness, vomiting, прогрессия в Heat Stroke. Тут ядро выглядит рабочим. Но лекарства типа electrolytes/rehydration работают скорее через общий hydration support/cure timer, а не через полноценное “снять симптомы heat exhaustion”.</t>
+  </si>
+  <si>
+    <t>Heat Stroke</t>
+  </si>
+  <si>
+    <t>Появляется как прогрессия из Heat Exhaustion. Есть collapse/confusion/thirst и летальность. Главная проблема: cooling блокирует recovery, но death check не учитывает “уже охлаждаюсь/лечусь” так же явно, как hypothermia учитывает тепло. То есть риск смерти может быть слишком тупым и старомодным.</t>
+  </si>
+  <si>
+    <t>Dysentery</t>
+  </si>
+  <si>
+    <r>
+      <t>Триггер через новую body temperature систему есть: опасная зона ниже 34C, плюс fallback через холод/мокроту. Выздоровление правильно требует тепло. Но симптомы самой болезни слабовато применяются: </t>
     </r>
     <r>
       <rPr>
@@ -353,7 +585,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>6+</t>
+      <t>temperatureDrain</t>
     </r>
     <r>
       <rPr>
@@ -361,12 +593,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t> доз;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>имеет интервал между дозами больше </t>
+      <t> и </t>
     </r>
     <r>
       <rPr>
@@ -374,7 +601,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>0</t>
+      <t>staminaPenalty</t>
     </r>
     <r>
       <rPr>
@@ -382,12 +609,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>То есть большинство </t>
+      <t> прописаны в definition, но в environmental effect handler они фактически не обрабатываются. Основное ощущение холода, вероятно, идёт из </t>
     </r>
     <r>
       <rPr>
@@ -395,7 +617,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>tier 3</t>
+      <t>EHR_BodyTemperature</t>
     </r>
     <r>
       <rPr>
@@ -403,7 +625,12 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t> не ловят передоз, потому что они одноразовые: IV, инъекции, emergency kit, </t>
+      <t>, а не из disease stage.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Триггер есть, но узкий: сейчас hook ловит </t>
     </r>
     <r>
       <rPr>
@@ -411,7 +638,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>doseInterval = 0</t>
+      <t>ISDrinkFromBottle</t>
     </r>
     <r>
       <rPr>
@@ -419,7 +646,7 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>, </t>
+      <t> и tainted water. Прямые источники типа river/toilet/tap/rainCollector в коде рассчитаны, но я не вижу реального hook-а, который передаёт эти sourceType из мира. Симптомы есть: thirst/hunger drain, vomiting, blood loss. Но anti-diarrheal почти наверняка не влияет на core drain, потому что </t>
     </r>
     <r>
       <rPr>
@@ -427,7 +654,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>dosesRequired = 1</t>
+      <t>diarrhea</t>
     </r>
     <r>
       <rPr>
@@ -435,657 +662,6 @@
         <rFont val="Segoe UI"/>
         <family val="2"/>
       </rPr>
-      <t>. Исключение среди tier 3 сейчас: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>RifampicinComboPack</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> - там </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>24h</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>14 доз</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, значит ранний прием может дать передоз. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>RespiratorySupportKit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> не должен давать передоз, потому что там всего </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> дозы.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>вешается </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>medication_overdose</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> на </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>8-10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> часов;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>если уже есть передоз и бахнуть еще раз, intensity усиливается до капа </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SICKNESS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> до </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>46-54%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>FOOD_SICKNESS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> до </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>46-50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>THIRST</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> до </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>68-76%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ENDURANCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> капается до </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>53-45%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>HP режется примерно до </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>63/56/49</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> в зависимости от intensity.</t>
-    </r>
-  </si>
-  <si>
-    <t>PEREDOS</t>
-  </si>
-  <si>
-    <t>(ПЕРЕЧЕКАТЬ ВСЕ)</t>
-  </si>
-  <si>
-    <t>добавить fever для других болезней</t>
-  </si>
-  <si>
-    <r>
-      <t>Antipyretic Tablets</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>: 12 доз в упаковке, OTC tier 1, действует 4 игровых часа, снижает именно болезнь-ассоциированный fever и не должен охлаждать обычный перегрев/жару от окружения.</t>
-    </r>
-  </si>
-  <si>
-    <t>Симптомы: жажда на 2 стадии, кашель, жар/sickness, слабость, просадка endurance, дыхательные проблемы; на поздней стадии без лечения может бить по HP и быть летальной.</t>
-  </si>
-  <si>
-    <t>Применение для cotton balls/затыкать кровотечение (пак)</t>
-  </si>
-  <si>
-    <t>Кашель в платок?</t>
-  </si>
-  <si>
-    <t>Новый перк: хирург</t>
-  </si>
-  <si>
-    <t>сделать реальный флаер с картинками</t>
-  </si>
-  <si>
-    <t>новый перк: не может поднять медицину выше 1, не получает знания с журнала</t>
-  </si>
-  <si>
-    <t>Минимальное разрешение окна</t>
-  </si>
-  <si>
-    <t>headache</t>
-  </si>
-  <si>
-    <t>добавить стресс болезнь</t>
-  </si>
-  <si>
-    <t>добавить депресуху болезнь</t>
-  </si>
-  <si>
-    <t>add immunity system later</t>
-  </si>
-  <si>
-    <t>Дистрибуция крови, добавить anti dizziness препарат, баланс длительности болезней, broken legs, проверить каждую еду на food poison, антидепресант механика которая убирает накопление депрессии на неделю-две, перевести все болезни на мудл фреймворк?, radio frequency, добавить остаточное кровотечение снижающееся со временем, убрать флаг с грибного тубика, новый UI с иконками по красивому, посмотреть на темперапуру при тричиносисе, проверить водителя которого укачивает, переделать механику severity, добавить какие-то бустеры на подобии caffeine pills, крафт лекарств, проверить препараты на побочки без болени, поддержка drug mod (выпилить скорее всего), новые бандажи (упаковка), медицинский спирт</t>
-  </si>
-  <si>
-    <t>прочекать еще раз все 3 фуд болезни</t>
-  </si>
-  <si>
-    <t>проверить все сырое мясо на работоспособность РЫБА</t>
-  </si>
-  <si>
-    <t>добавить в сендбокс опции по отключениям болезней</t>
-  </si>
-  <si>
-    <t>diziness to CAR</t>
-  </si>
-  <si>
-    <t>Alchoholic Intoxication</t>
-  </si>
-  <si>
-    <t>Добавить иконки под overview/Active Medication/SideEffects</t>
-  </si>
-  <si>
-    <t>Добавить в карточку болезни симптомы если навык или книжка есть</t>
-  </si>
-  <si>
-    <t>проверить чтобы все лечащие препараты заметно снижали симптомы</t>
-  </si>
-  <si>
-    <t>TB antibiotics no active in UI</t>
-  </si>
-  <si>
-    <t>Compact mode</t>
-  </si>
-  <si>
-    <t>добавить все мед журналы на каждую болезнь</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check doctor skill </t>
-  </si>
-  <si>
-    <t>Заменить /добавить нормальные painkillers</t>
-  </si>
-  <si>
-    <t>Wound Infection</t>
-  </si>
-  <si>
-    <t>nothing</t>
-  </si>
-  <si>
-    <t>pain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pain, fever (38) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sepsis trigger, increased pain, fever </t>
-  </si>
-  <si>
-    <t>Cure:</t>
-  </si>
-  <si>
-    <t>Relieve</t>
-  </si>
-  <si>
-    <t>Anti-Inflammatory, anyipyretic</t>
-  </si>
-  <si>
-    <t>Antibiotic Ointment, Broad Spectrum, IV antibiotics</t>
-  </si>
-  <si>
-    <t>р</t>
-  </si>
-  <si>
-    <t>Возможно добавить в журнал описание овердоза препаратами</t>
-  </si>
-  <si>
-    <t>Можно добавить звук на применение препаратов</t>
-  </si>
-  <si>
-    <t>И анимации</t>
-  </si>
-  <si>
-    <t>Sepsis</t>
-  </si>
-  <si>
-    <t>Cure</t>
-  </si>
-  <si>
-    <t>IV Antibiotics, Metronizadole, vancomycin, emergency sepsis kit</t>
-  </si>
-  <si>
-    <t>Fever (38) hp 85%</t>
-  </si>
-  <si>
-    <t>Fever (38.6, fatigue 50, hp 65, stress sometimes</t>
-  </si>
-  <si>
-    <t>Fever 39.4 fatigue 70, hp 30</t>
-  </si>
-  <si>
-    <t>Fever 40 fatigue 80, hp death</t>
-  </si>
-  <si>
-    <t>Одежда не обновляется в INFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tetanus </t>
-  </si>
-  <si>
-    <t>deep wound + glass in wound</t>
-  </si>
-  <si>
-    <t>neck pain, hp30%, end 70%</t>
-  </si>
-  <si>
-    <t>body pain, fever 39, fall,hp damage, edn 50%</t>
-  </si>
-  <si>
-    <t>probably death</t>
-  </si>
-  <si>
-    <t>TetanusAntitoxin, tetanus immunoglobin</t>
-  </si>
-  <si>
-    <t>cure</t>
-  </si>
-  <si>
-    <t>Muscle relaxant, intiinflammatory, antipyretic</t>
-  </si>
-  <si>
-    <t>Prescribed Painkillers addiction</t>
-  </si>
-  <si>
-    <t>reliefe</t>
-  </si>
-  <si>
-    <t>intiinflammatory, antipyretic?</t>
-  </si>
-  <si>
-    <t>icon</t>
-  </si>
-  <si>
-    <t>AntiSecpit cream prevents</t>
-  </si>
-  <si>
-    <t>Antibiotic Ointment</t>
-  </si>
-  <si>
-    <t>"-'</t>
-  </si>
-  <si>
-    <t>Add boost pills, 100% fatigue later</t>
-  </si>
-  <si>
-    <t>Cancer when smoking?</t>
-  </si>
-  <si>
-    <t>Новый перк:нельзя заразить рану</t>
-  </si>
-  <si>
-    <t>Обернуть sleeping pills в тот же UI</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>Bandage были в приоритете над pain</t>
-  </si>
-  <si>
-    <r>
-      <t>если EHR уже увидел infection и завел инкубацию, заживление самой поверхностной раны больше не отменяет болезнь. Отменить инкубацию должен только явный early disinfect/antiseptic путь, иначе через 12 часов она станет </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>Wound Infection</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Bite in the eye mechanics so character can be blind</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>Сделать Cellulitis в справочнике как WIP</t>
-  </si>
-  <si>
-    <t>чек новый овердоз</t>
-  </si>
-  <si>
-    <t>Blood bags fresh all the time</t>
-  </si>
-  <si>
-    <t>gene therapy adds perk</t>
-  </si>
-  <si>
-    <t>Plant Remedies</t>
-  </si>
-  <si>
-    <t>Common Cold</t>
-  </si>
-  <si>
-    <t>Hypothermia</t>
-  </si>
-  <si>
-    <t>Heat Exhaustion</t>
-  </si>
-  <si>
-    <t>Триггер есть через body temp выше 40.5C или fallback hot exposure. Есть жажда, судороги, dizziness, vomiting, прогрессия в Heat Stroke. Тут ядро выглядит рабочим. Но лекарства типа electrolytes/rehydration работают скорее через общий hydration support/cure timer, а не через полноценное “снять симптомы heat exhaustion”.</t>
-  </si>
-  <si>
-    <t>Heat Stroke</t>
-  </si>
-  <si>
-    <t>Появляется как прогрессия из Heat Exhaustion. Есть collapse/confusion/thirst и летальность. Главная проблема: cooling блокирует recovery, но death check не учитывает “уже охлаждаюсь/лечусь” так же явно, как hypothermia учитывает тепло. То есть риск смерти может быть слишком тупым и старомодным.</t>
-  </si>
-  <si>
-    <t>Dysentery</t>
-  </si>
-  <si>
-    <r>
-      <t>Триггер через новую body temperature систему есть: опасная зона ниже 34C, плюс fallback через холод/мокроту. Выздоровление правильно требует тепло. Но симптомы самой болезни слабовато применяются: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>temperatureDrain</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> и </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>staminaPenalty</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> прописаны в definition, но в environmental effect handler они фактически не обрабатываются. Основное ощущение холода, вероятно, идёт из </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>EHR_BodyTemperature</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>, а не из disease stage.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Триггер есть, но узкий: сейчас hook ловит </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>ISDrinkFromBottle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> и tainted water. Прямые источники типа river/toilet/tap/rainCollector в коде рассчитаны, но я не вижу реального hook-а, который передаёт эти sourceType из мира. Симптомы есть: thirst/hunger drain, vomiting, blood loss. Но anti-diarrheal почти наверняка не влияет на core drain, потому что </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>diarrhea</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
       <t> reduction нигде в environmental effect handler не читается. Летальность через dehydration оставлена ванили: мод просто держит thirst на максимуме, сам HP не добивает.</t>
     </r>
   </si>
@@ -1106,9 +682,6 @@
   </si>
   <si>
     <t>Add medical watches that required to see blood level</t>
-  </si>
-  <si>
-    <t>Ванная</t>
   </si>
   <si>
     <t>Стадия 1 почти без видимых эффектов, фразы/sniff.
@@ -1294,17 +867,74 @@
 По лечению нужно будет добавить несколько новых препаратов: IV Fluids, курс 24 часа (Item_IVFluids.png), Furosemide, курс 48 часов (.png) Side Effect - Dehydration(high thirst), lower back pain.   </t>
   </si>
   <si>
-    <t>influenza?</t>
-  </si>
-  <si>
-    <t>spoiled bags can be used and triggers AHTR</t>
+    <t>Blood Loss Shock</t>
+  </si>
+  <si>
+    <t>Salmonellosis</t>
+  </si>
+  <si>
+    <t>Сырые яйца</t>
+  </si>
+  <si>
+    <t>Rat-bite Fever</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>при луте мусорных контейнеров</t>
+  </si>
+  <si>
+    <t>Concussion</t>
+  </si>
+  <si>
+    <t>Падение</t>
+  </si>
+  <si>
+    <t>Delirium</t>
+  </si>
+  <si>
+    <t>Психическая болезнь с приколами</t>
+  </si>
+  <si>
+    <t>Pain Shock</t>
+  </si>
+  <si>
+    <t>Insomnia</t>
+  </si>
+  <si>
+    <t>Depression</t>
+  </si>
+  <si>
+    <t>Prescripted Antidepressants</t>
+  </si>
+  <si>
+    <t>Adrenaline</t>
+  </si>
+  <si>
+    <t>Speed Boost/panic 0%</t>
+  </si>
+  <si>
+    <t>Dehydration 2 hours later</t>
+  </si>
+  <si>
+    <t>Homemade Herbal Tea</t>
+  </si>
+  <si>
+    <t>Cold Treatment</t>
+  </si>
+  <si>
+    <t>Neuro Stabilizer</t>
+  </si>
+  <si>
+    <t>stress/panic 0%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1398,6 +1028,13 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1419,7 +1056,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1476,6 +1113,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2344,7 +1982,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
@@ -2497,9 +2135,7 @@
       <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="U26" s="3"/>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
@@ -2534,7 +2170,7 @@
     </row>
     <row r="34" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
@@ -2542,7 +2178,7 @@
         <v>50</v>
       </c>
       <c r="U35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="2:21" ht="16.5" x14ac:dyDescent="0.25">
@@ -2567,18 +2203,18 @@
         <v>55</v>
       </c>
       <c r="U39" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B40" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="U40" s="3"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U42" s="3" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2596,13 +2232,13 @@
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2610,10 +2246,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="H4" s="21"/>
       <c r="I4" s="21"/>
@@ -2632,7 +2268,7 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21"/>
@@ -2652,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
@@ -2669,10 +2305,10 @@
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
@@ -2689,10 +2325,10 @@
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
@@ -2709,7 +2345,7 @@
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
@@ -2772,13 +2408,13 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
@@ -2786,7 +2422,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
@@ -2794,7 +2430,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
@@ -2802,34 +2438,34 @@
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
@@ -2837,7 +2473,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
@@ -2845,7 +2481,7 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
@@ -2853,28 +2489,28 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E34" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2895,63 +2531,63 @@
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="18" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="20" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="2:8" ht="115.5" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
@@ -2962,12 +2598,12 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="17" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="99" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
@@ -2978,15 +2614,13 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
@@ -2997,12 +2631,12 @@
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="16" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3034,10 +2668,10 @@
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
@@ -3048,7 +2682,7 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
@@ -3059,17 +2693,17 @@
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="255" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -3083,74 +2717,69 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D345CE2-5F04-48E0-AE34-8739DA490F25}">
-  <dimension ref="B3:M28"/>
+  <dimension ref="B3:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="61.85546875" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="23" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="C3" s="15"/>
     </row>
-    <row r="4" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="23"/>
       <c r="C4" s="15"/>
     </row>
-    <row r="5" spans="2:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="23"/>
       <c r="C5" s="15"/>
     </row>
-    <row r="6" spans="2:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="23"/>
       <c r="C6" s="15"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="23"/>
       <c r="C7" s="15"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="23"/>
       <c r="C8" s="15"/>
-      <c r="M8" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="23"/>
       <c r="C9" s="15"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
-      <c r="F11" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
     </row>
@@ -3217,42 +2846,42 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="3"/>
       <c r="G3" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3"/>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3260,40 +2889,40 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="3:23" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C21" s="10" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
@@ -3304,108 +2933,108 @@
     </row>
     <row r="24" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C24" s="10" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C25" s="10" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C26" s="10" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C27" s="10" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C29" s="10" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C31" s="10" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="N31" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="3:23" x14ac:dyDescent="0.25">
       <c r="W32" s="3" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="3:23" x14ac:dyDescent="0.25">
       <c r="H33" s="3" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="W34" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="3:23" x14ac:dyDescent="0.25">
       <c r="W35" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="3:23" x14ac:dyDescent="0.25">
       <c r="K41" s="3" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="3:23" x14ac:dyDescent="0.25">
       <c r="W42" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C43" s="3" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="F43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="3:23" x14ac:dyDescent="0.25">
       <c r="F44" s="3" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="3:23" x14ac:dyDescent="0.25">
       <c r="F45" s="3"/>
       <c r="K45" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="3:23" x14ac:dyDescent="0.25">
@@ -3413,53 +3042,53 @@
     </row>
     <row r="47" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I48" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C49" s="3" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="3:18" x14ac:dyDescent="0.25">
       <c r="R50" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="3:18" x14ac:dyDescent="0.25">
       <c r="P54" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G55" s="3" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="P55" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G61" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="O61" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G62" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="15:15" x14ac:dyDescent="0.25">
       <c r="O65" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3471,126 +3100,162 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
-  <dimension ref="B3:Z32"/>
+  <dimension ref="B3:Z42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
-        <v>66</v>
-      </c>
+      <c r="B4" s="8"/>
     </row>
     <row r="5" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="B5" s="7"/>
     </row>
     <row r="6" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
-        <v>67</v>
-      </c>
+      <c r="B6" s="7"/>
     </row>
     <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>68</v>
-      </c>
+      <c r="B7" s="7"/>
     </row>
     <row r="8" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
-        <v>60</v>
-      </c>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
-        <v>69</v>
-      </c>
+      <c r="B9" s="8"/>
     </row>
     <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="B10" s="8"/>
     </row>
     <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="B11" s="7"/>
     </row>
     <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
-        <v>63</v>
-      </c>
+      <c r="B12" s="7"/>
     </row>
     <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>70</v>
-      </c>
+      <c r="B13" s="7"/>
     </row>
     <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>64</v>
-      </c>
+      <c r="B14" s="7"/>
     </row>
     <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="B15" s="7"/>
     </row>
     <row r="16" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
-        <v>74</v>
-      </c>
+      <c r="B16" s="8"/>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B17" s="9"/>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B18" s="9"/>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B19" s="9"/>
       <c r="U19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>75</v>
-      </c>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B20" s="9"/>
     </row>
     <row r="21" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>76</v>
+      <c r="B21" s="7"/>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" t="s">
+        <v>189</v>
+      </c>
+      <c r="L22" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>186</v>
+      </c>
+      <c r="F24" t="s">
+        <v>187</v>
+      </c>
+      <c r="L24" t="s">
+        <v>183</v>
+      </c>
+      <c r="N24" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
       <c r="X27" s="3" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="Z27" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="H28" t="s">
+        <v>169</v>
+      </c>
       <c r="T28" t="s">
-        <v>138</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="H30" t="s">
+        <v>170</v>
+      </c>
+      <c r="J30" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="V32" t="s">
-        <v>142</v>
+      <c r="H32" t="s">
+        <v>172</v>
+      </c>
+      <c r="I32" t="s">
+        <v>173</v>
+      </c>
+      <c r="J32" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H34" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H36" t="s">
+        <v>177</v>
+      </c>
+      <c r="J36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H38" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H42" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43360C05-6C01-4B38-AFA0-27D62E734630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B69A50-14E4-48AD-8882-6041FC80AD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3180" windowWidth="28800" windowHeight="14355" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="3180" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Environmental " sheetId="7" r:id="rId4"/>
     <sheet name="Blood" sheetId="8" r:id="rId5"/>
     <sheet name="Не забыть" sheetId="5" r:id="rId6"/>
-    <sheet name="Mechanics" sheetId="3" r:id="rId7"/>
+    <sheet name="RadioDialogues" sheetId="9" r:id="rId7"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="196">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -324,18 +325,9 @@
     <t>Кашель в платок?</t>
   </si>
   <si>
-    <t>Новый перк: хирург</t>
-  </si>
-  <si>
     <t>сделать реальный флаер с картинками</t>
   </si>
   <si>
-    <t>новый перк: не может поднять медицину выше 1, не получает знания с журнала</t>
-  </si>
-  <si>
-    <t>Минимальное разрешение окна</t>
-  </si>
-  <si>
     <t>headache</t>
   </si>
   <si>
@@ -366,30 +358,15 @@
     <t>Alchoholic Intoxication</t>
   </si>
   <si>
-    <t>Добавить иконки под overview/Active Medication/SideEffects</t>
-  </si>
-  <si>
-    <t>Добавить в карточку болезни симптомы если навык или книжка есть</t>
-  </si>
-  <si>
     <t>проверить чтобы все лечащие препараты заметно снижали симптомы</t>
   </si>
   <si>
     <t>TB antibiotics no active in UI</t>
   </si>
   <si>
-    <t>Compact mode</t>
-  </si>
-  <si>
     <t>добавить все мед журналы на каждую болезнь</t>
   </si>
   <si>
-    <t xml:space="preserve">Check doctor skill </t>
-  </si>
-  <si>
-    <t>Заменить /добавить нормальные painkillers</t>
-  </si>
-  <si>
     <t>Wound Infection</t>
   </si>
   <si>
@@ -450,9 +427,6 @@
     <t>Fever 40 fatigue 80, hp death</t>
   </si>
   <si>
-    <t>Одежда не обновляется в INFO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tetanus </t>
   </si>
   <si>
@@ -486,31 +460,16 @@
     <t>intiinflammatory, antipyretic?</t>
   </si>
   <si>
-    <t>icon</t>
-  </si>
-  <si>
     <t>AntiSecpit cream prevents</t>
   </si>
   <si>
-    <t>Antibiotic Ointment</t>
-  </si>
-  <si>
     <t>"-'</t>
   </si>
   <si>
     <t>Cancer when smoking?</t>
   </si>
   <si>
-    <t>Новый перк:нельзя заразить рану</t>
-  </si>
-  <si>
     <t>Обернуть sleeping pills в тот же UI</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>Bandage были в приоритете над pain</t>
   </si>
   <si>
     <r>
@@ -541,15 +500,6 @@
   </si>
   <si>
     <t>Сделать Cellulitis в справочнике как WIP</t>
-  </si>
-  <si>
-    <t>чек новый овердоз</t>
-  </si>
-  <si>
-    <t>Blood bags fresh all the time</t>
-  </si>
-  <si>
-    <t>gene therapy adds perk</t>
   </si>
   <si>
     <t>Plant Remedies</t>
@@ -842,16 +792,7 @@
     <t>Возможно поменять HeatExposure с 33 градусов</t>
   </si>
   <si>
-    <t>Укус насекомого? Если очень долго сидеть на траве</t>
-  </si>
-  <si>
-    <t>Чекнуть perk cost</t>
-  </si>
-  <si>
     <t>Antibodies mod compability</t>
-  </si>
-  <si>
-    <t>Blood Types Compability hidden behind flyer</t>
   </si>
   <si>
     <t>Добавить after bleed</t>
@@ -915,9 +856,6 @@
     <t>Speed Boost/panic 0%</t>
   </si>
   <si>
-    <t>Dehydration 2 hours later</t>
-  </si>
-  <si>
     <t>Homemade Herbal Tea</t>
   </si>
   <si>
@@ -928,13 +866,94 @@
   </si>
   <si>
     <t>stress/panic 0%</t>
+  </si>
+  <si>
+    <t>EHR Doctor</t>
+  </si>
+  <si>
+    <t>First Aid 6</t>
+  </si>
+  <si>
+    <t>1 short blade</t>
+  </si>
+  <si>
+    <t>5/5 str/fit</t>
+  </si>
+  <si>
+    <t>Knows all diseases</t>
+  </si>
+  <si>
+    <t>0 points left</t>
+  </si>
+  <si>
+    <t>EHR Surgeon</t>
+  </si>
+  <si>
+    <t>First Aid 10</t>
+  </si>
+  <si>
+    <t>3 Short blade</t>
+  </si>
+  <si>
+    <t>Scalpel Master</t>
+  </si>
+  <si>
+    <t>x100 scalpel durability</t>
+  </si>
+  <si>
+    <t>x3 damage</t>
+  </si>
+  <si>
+    <t>perk</t>
+  </si>
+  <si>
+    <t>5/5 fit str</t>
+  </si>
+  <si>
+    <t>"-" 8 points</t>
+  </si>
+  <si>
+    <t>radio frequency</t>
+  </si>
+  <si>
+    <t>добавить остаточное кровотечение снижающееся со временем</t>
+  </si>
+  <si>
+    <t>Tuberculosis?</t>
+  </si>
+  <si>
+    <t>lavender fresh</t>
+  </si>
+  <si>
+    <t>ginger root</t>
+  </si>
+  <si>
+    <t>Ceramic mortar</t>
+  </si>
+  <si>
+    <t>Morarr and pestle</t>
+  </si>
+  <si>
+    <t>Garlic (fresh)</t>
+  </si>
+  <si>
+    <t>Oregano (fresh)</t>
+  </si>
+  <si>
+    <t>Thyme (Fresh)</t>
+  </si>
+  <si>
+    <t>Доделать Cellulitis</t>
+  </si>
+  <si>
+    <t>Add loot to gigamart</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1035,6 +1054,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1056,7 +1102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1104,6 +1150,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1113,7 +1160,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1982,7 +2034,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
@@ -2232,13 +2284,13 @@
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2246,175 +2298,175 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
+        <v>79</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
+        <v>80</v>
+      </c>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
+        <v>81</v>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
+        <v>85</v>
+      </c>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
+        <v>84</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
+        <v>108</v>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
@@ -2422,7 +2474,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
@@ -2430,7 +2482,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
@@ -2438,34 +2490,34 @@
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
@@ -2473,7 +2525,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
@@ -2481,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
@@ -2489,28 +2541,28 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2531,63 +2583,63 @@
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="18" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="20" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="2:8" ht="115.5" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
@@ -2598,12 +2650,12 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="17" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="99" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
@@ -2614,13 +2666,13 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="17" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
@@ -2631,79 +2683,79 @@
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="16" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>142</v>
+      <c r="B32" s="23" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="22"/>
+      <c r="B33" s="23"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="22"/>
+      <c r="B34" s="23"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="22"/>
+      <c r="B35" s="23"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="22"/>
+      <c r="B36" s="23"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="22"/>
+      <c r="B37" s="23"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="22"/>
+      <c r="B38" s="23"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="22"/>
+      <c r="B39" s="23"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="22"/>
+      <c r="B40" s="23"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="22"/>
+      <c r="B41" s="23"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
+        <v>126</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>147</v>
-      </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
+        <v>130</v>
+      </c>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="255" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2725,33 +2777,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
-        <v>168</v>
+      <c r="B3" s="24" t="s">
+        <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="23"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="23"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="23"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="23"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="23"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -2841,88 +2893,61 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="A2:W65"/>
+  <dimension ref="B2:W61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C3" s="3"/>
-      <c r="G3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C4" s="3"/>
-      <c r="G4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>161</v>
-      </c>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G7" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H10" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" t="s">
-        <v>122</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I14" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="3:23" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C21" s="10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
@@ -2930,59 +2955,66 @@
     </row>
     <row r="23" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C23" s="10"/>
+      <c r="K23" s="3" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="24" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C24" s="10" t="s">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C25" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C26" s="10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C27" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C29" s="26" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C29" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
     <row r="31" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C31" s="10" t="s">
-        <v>76</v>
+      <c r="C31" s="26" t="s">
+        <v>73</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N31" t="s">
         <v>129</v>
       </c>
+      <c r="N31" s="27" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="32" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="N32" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="W32" s="3" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="H33" s="3" t="s">
-        <v>130</v>
-      </c>
+      <c r="H33" s="3"/>
     </row>
     <row r="34" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="W34" t="s">
         <v>61</v>
@@ -2990,105 +3022,85 @@
     </row>
     <row r="35" spans="3:23" x14ac:dyDescent="0.25">
       <c r="W35" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="D39" t="s">
-        <v>84</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="K39" s="3"/>
     </row>
     <row r="41" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="K41" s="3" t="s">
-        <v>133</v>
+      <c r="K41" s="27" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="3:23" x14ac:dyDescent="0.25">
       <c r="W42" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C43" s="3" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="F43" s="3"/>
-      <c r="K43" s="3" t="s">
-        <v>159</v>
+      <c r="K43" s="27" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="F44" s="3" t="s">
-        <v>162</v>
-      </c>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" spans="3:23" x14ac:dyDescent="0.25">
       <c r="F45" s="3"/>
       <c r="K45" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="3:23" x14ac:dyDescent="0.25">
       <c r="R46" s="3"/>
     </row>
     <row r="47" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C47" t="s">
-        <v>163</v>
+      <c r="C47" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="I48" s="3" t="s">
-        <v>132</v>
-      </c>
+      <c r="I48" s="3"/>
     </row>
     <row r="49" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C49" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="C49" s="3"/>
     </row>
     <row r="50" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="D50" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="R50" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="3:18" x14ac:dyDescent="0.25">
       <c r="P54" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="G55" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="G55" s="3"/>
       <c r="P55" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G61" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="O61" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="G62" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O65" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3099,63 +3111,287 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A4C555-5941-44D5-8766-80774E93DFFB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="89.28515625" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
   <dimension ref="B3:Z42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+    </row>
+    <row r="4" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
-    </row>
-    <row r="5" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M4" s="25"/>
+      <c r="N4" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+    </row>
+    <row r="5" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+    </row>
+    <row r="6" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B6" s="7"/>
-    </row>
-    <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+    </row>
+    <row r="7" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="7"/>
-    </row>
-    <row r="8" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+    </row>
+    <row r="8" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="7"/>
-    </row>
-    <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+    </row>
+    <row r="9" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="8"/>
-    </row>
-    <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M9" s="25"/>
+      <c r="N9" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="O9" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+    </row>
+    <row r="10" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="8"/>
-    </row>
-    <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+    </row>
+    <row r="11" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="7"/>
-    </row>
-    <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+    </row>
+    <row r="12" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="7"/>
-    </row>
-    <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M12" s="25"/>
+      <c r="N12" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="O12" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+    </row>
+    <row r="13" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="7"/>
-    </row>
-    <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+    </row>
+    <row r="14" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="7"/>
-    </row>
-    <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+    </row>
+    <row r="15" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="7"/>
-    </row>
-    <row r="16" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+    </row>
+    <row r="16" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B19" s="9"/>
-      <c r="U19" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B20" s="9"/>
@@ -3165,97 +3401,118 @@
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="E22" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F24" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="L24" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="N24" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>185</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="S26" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="X27" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="S27" t="s">
+        <v>192</v>
+      </c>
+      <c r="X27" s="3"/>
       <c r="Z27" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>169</v>
-      </c>
-      <c r="T28" t="s">
-        <v>117</v>
+        <v>149</v>
+      </c>
+      <c r="S28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="S29" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.25">
       <c r="H30" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="J30" t="s">
-        <v>171</v>
+        <v>151</v>
+      </c>
+      <c r="S30" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.25">
       <c r="H32" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="I32" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="J32" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="34" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H34" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="36" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H36" t="s">
-        <v>177</v>
-      </c>
-      <c r="J36" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="38" spans="8:10" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="S32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="S33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="H34" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="H36" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="K36" s="25"/>
+    </row>
+    <row r="38" spans="8:19" x14ac:dyDescent="0.25">
       <c r="H38" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="40" spans="8:10" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="8:19" x14ac:dyDescent="0.25">
       <c r="H40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="42" spans="8:10" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="8:19" x14ac:dyDescent="0.25">
       <c r="H42" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B69A50-14E4-48AD-8882-6041FC80AD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C0AAE9-9762-421E-8B33-3CDFE8E82D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3180" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="197">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -948,12 +948,15 @@
   <si>
     <t>Add loot to gigamart</t>
   </si>
+  <si>
+    <t>Funriture rest bonus</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,6 +1084,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1102,7 +1111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1151,6 +1160,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1160,12 +1175,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2300,20 +2312,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2322,18 +2334,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2342,18 +2354,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -2362,18 +2374,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -2382,78 +2394,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -2687,61 +2699,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="27" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="23"/>
+      <c r="B33" s="27"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="23"/>
+      <c r="B34" s="27"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="23"/>
+      <c r="B35" s="27"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="23"/>
+      <c r="B36" s="27"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="23"/>
+      <c r="B37" s="27"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="23"/>
+      <c r="B38" s="27"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="23"/>
+      <c r="B39" s="27"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="23"/>
+      <c r="B40" s="27"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="23"/>
+      <c r="B41" s="27"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -2777,33 +2789,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="28" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="24"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="24"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="24"/>
+      <c r="B6" s="28"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="24"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="24"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="24"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -2897,6 +2909,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
+        <v>196</v>
+      </c>
       <c r="G2" s="3" t="s">
         <v>195</v>
       </c>
@@ -2913,12 +2928,12 @@
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="25" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2926,7 +2941,7 @@
       <c r="H10" s="3"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+      <c r="B12" s="21" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2963,7 +2978,7 @@
       <c r="C24" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" s="21" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2983,18 +2998,18 @@
       </c>
     </row>
     <row r="29" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="29" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="23" t="s">
         <v>73</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="N31" s="27" t="s">
+      <c r="N31" s="24" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3027,7 +3042,7 @@
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I36" s="3"/>
-      <c r="L36" s="3" t="s">
+      <c r="L36" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3035,7 +3050,7 @@
       <c r="K39" s="3"/>
     </row>
     <row r="41" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="K41" s="27" t="s">
+      <c r="K41" s="24" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3045,11 +3060,11 @@
       </c>
     </row>
     <row r="43" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="21" t="s">
         <v>147</v>
       </c>
       <c r="F43" s="3"/>
-      <c r="K43" s="27" t="s">
+      <c r="K43" s="24" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3066,7 +3081,7 @@
       <c r="R46" s="3"/>
     </row>
     <row r="47" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="21" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3132,260 +3147,260 @@
   <sheetData>
     <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C3" s="3"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
     </row>
     <row r="4" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25" t="s">
+      <c r="M4" s="22"/>
+      <c r="N4" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="O4" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
     </row>
     <row r="5" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25" t="s">
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
     </row>
     <row r="6" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B6" s="7"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25" t="s">
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="25"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="25"/>
-      <c r="X6" s="25"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
     </row>
     <row r="7" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="7"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25" t="s">
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="25"/>
-      <c r="V7" s="25"/>
-      <c r="W7" s="25"/>
-      <c r="X7" s="25"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
     </row>
     <row r="8" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="7"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25" t="s">
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="25"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
     </row>
     <row r="9" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="8"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25" t="s">
+      <c r="M9" s="22"/>
+      <c r="N9" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="O9" s="25" t="s">
+      <c r="O9" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
     </row>
     <row r="10" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="8"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25" t="s">
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="25"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
     </row>
     <row r="11" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="7"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25" t="s">
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
     </row>
     <row r="12" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="7"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25" t="s">
+      <c r="M12" s="22"/>
+      <c r="N12" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="O12" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25" t="s">
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-      <c r="X12" s="25"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
     </row>
     <row r="13" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="7"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25" t="s">
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25" t="s">
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="25"/>
-      <c r="X13" s="25"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
     </row>
     <row r="14" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="7"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25" t="s">
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-      <c r="X14" s="25"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
     </row>
     <row r="15" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="7"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
     </row>
     <row r="16" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="25"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
@@ -3491,14 +3506,14 @@
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H36" s="25" t="s">
+      <c r="H36" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25" t="s">
+      <c r="I36" s="22"/>
+      <c r="J36" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="K36" s="25"/>
+      <c r="K36" s="22"/>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.25">
       <c r="H38" t="s">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C0AAE9-9762-421E-8B33-3CDFE8E82D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5338105A-4C88-4CF2-AD63-A37FB93508F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="208">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -950,6 +950,39 @@
   </si>
   <si>
     <t>Funriture rest bonus</t>
+  </si>
+  <si>
+    <t>1. Медицна не дает болзень смотетьб</t>
+  </si>
+  <si>
+    <t>2. Шизу слышна всем</t>
+  </si>
+  <si>
+    <t>3. Медикаменты не показываются</t>
+  </si>
+  <si>
+    <t>4 не апдейтися сразу</t>
+  </si>
+  <si>
+    <t>5. Тетанус не прокает</t>
+  </si>
+  <si>
+    <t>6. Кровь очень медленно снижается</t>
+  </si>
+  <si>
+    <t>7 Странно синхронизируется травмы</t>
+  </si>
+  <si>
+    <t>пациент зеро нету</t>
+  </si>
+  <si>
+    <t>питье с параши не дает болезнь</t>
+  </si>
+  <si>
+    <t>cadeveric  без кашля</t>
+  </si>
+  <si>
+    <t>Сместился курсор</t>
   </si>
 </sst>
 </file>
@@ -1166,6 +1199,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1174,9 +1210,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2312,20 +2345,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2334,18 +2367,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2354,18 +2387,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="R6" s="26"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -2374,18 +2407,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -2394,78 +2427,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="27"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -2699,61 +2732,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="28" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="27"/>
+      <c r="B33" s="28"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="27"/>
+      <c r="B34" s="28"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="27"/>
+      <c r="B35" s="28"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="27"/>
+      <c r="B36" s="28"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="27"/>
+      <c r="B37" s="28"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="27"/>
+      <c r="B38" s="28"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="27"/>
+      <c r="B39" s="28"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="27"/>
+      <c r="B40" s="28"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="27"/>
+      <c r="B41" s="28"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -2789,33 +2822,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="29" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="28"/>
+      <c r="B4" s="29"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="28"/>
+      <c r="B5" s="29"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="28"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="28"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="28"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="28"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -2922,37 +2955,80 @@
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C4" s="3"/>
     </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>197</v>
+      </c>
+    </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>198</v>
+      </c>
       <c r="G6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>199</v>
+      </c>
       <c r="G7" s="25" t="s">
         <v>63</v>
       </c>
     </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>200</v>
+      </c>
+    </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>201</v>
+      </c>
       <c r="G9" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>202</v>
+      </c>
       <c r="H10" s="3"/>
     </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>203</v>
+      </c>
+    </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
-        <v>76</v>
+      <c r="B12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>206</v>
+      </c>
       <c r="I14" s="3" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="3:23" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
         <v>64</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
@@ -2998,7 +3074,7 @@
       </c>
     </row>
     <row r="29" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="26" t="s">
         <v>71</v>
       </c>
     </row>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5338105A-4C88-4CF2-AD63-A37FB93508F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A5AC3D-3E65-4C5F-8CA8-179295C2D0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -946,9 +946,6 @@
     <t>Доделать Cellulitis</t>
   </si>
   <si>
-    <t>Add loot to gigamart</t>
-  </si>
-  <si>
     <t>Funriture rest bonus</t>
   </si>
   <si>
@@ -983,6 +980,9 @@
   </si>
   <si>
     <t>Сместился курсор</t>
+  </si>
+  <si>
+    <t>Defibrilator?</t>
   </si>
 </sst>
 </file>
@@ -2943,13 +2943,14 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="G2" s="3" t="s">
         <v>195</v>
       </c>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="25" t="s">
+        <v>207</v>
+      </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
@@ -2957,12 +2958,12 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G6" t="s">
         <v>74</v>
@@ -2970,7 +2971,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>63</v>
@@ -2978,12 +2979,12 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>75</v>
@@ -2991,28 +2992,28 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>186</v>
@@ -3020,7 +3021,7 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="3:23" x14ac:dyDescent="0.25">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A5AC3D-3E65-4C5F-8CA8-179295C2D0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C278062B-B8FF-4F8D-A935-70A7C1EEC48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="211">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -984,12 +984,21 @@
   <si>
     <t>Defibrilator?</t>
   </si>
+  <si>
+    <t>Добавить мед журнал insomnia</t>
+  </si>
+  <si>
+    <t>Добавить в мод оптион чтобы открывалась либо в компакт моде либо сразу в расширенном</t>
+  </si>
+  <si>
+    <t>there is a small bug that i got right away , if you use quick shower from lifestyle mod it doesnt end it just keeps going</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1123,6 +1132,12 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1144,7 +1159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1211,6 +1226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1673,55 +1689,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>29479</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>162521</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FCA23F4-7683-2C80-A33A-734BF96A886E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8181975" y="171450"/>
-          <a:ext cx="6477904" cy="4267796"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2938,30 +2905,39 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="B2:W61"/>
+  <dimension ref="B2:Y61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B2" s="25" t="s">
         <v>195</v>
       </c>
+      <c r="E2" s="25" t="s">
+        <v>209</v>
+      </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
         <v>207</v>
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>208</v>
+      </c>
       <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="Y4" s="30" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>197</v>
       </c>
@@ -2969,7 +2945,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>198</v>
       </c>
@@ -2977,12 +2953,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>200</v>
       </c>
@@ -2990,28 +2966,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>201</v>
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>205</v>
       </c>
@@ -3019,7 +2995,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>206</v>
       </c>
@@ -3198,7 +3174,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C278062B-B8FF-4F8D-A935-70A7C1EEC48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01585CEB-B431-49FD-ADCD-7497AA8E3393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="214">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -992,6 +992,15 @@
   </si>
   <si>
     <t>there is a small bug that i got right away , if you use quick shower from lifestyle mod it doesnt end it just keeps going</t>
+  </si>
+  <si>
+    <t>antibodies panel to her</t>
+  </si>
+  <si>
+    <t>Панелька закрывается у другого игрока нельзя зашить</t>
+  </si>
+  <si>
+    <t>Вытащить стекло и раны у меня рана зажившая, у игрока без изменений</t>
   </si>
 </sst>
 </file>
@@ -2933,12 +2942,15 @@
       </c>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="B5" s="22" t="s">
         <v>196</v>
       </c>
+      <c r="Y5" s="3" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="6" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="B6" s="22" t="s">
         <v>197</v>
       </c>
       <c r="G6" t="s">
@@ -2952,14 +2964,20 @@
       <c r="G7" s="25" t="s">
         <v>63</v>
       </c>
+      <c r="P7" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>199</v>
       </c>
+      <c r="P8" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>200</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -2967,7 +2985,7 @@
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>201</v>
       </c>
       <c r="H10" s="3"/>
@@ -2978,12 +2996,12 @@
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+      <c r="B12" s="22" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>204</v>
       </c>
     </row>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01585CEB-B431-49FD-ADCD-7497AA8E3393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FD016E-9849-429C-9ABE-106BB24D036F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="217">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1002,12 +1002,21 @@
   <si>
     <t>Вытащить стекло и раны у меня рана зажившая, у игрока без изменений</t>
   </si>
+  <si>
+    <t>Common cold от купания в ванной</t>
+  </si>
+  <si>
+    <t>overload when sitting health bug</t>
+  </si>
+  <si>
+    <t>i think i found a bug in b42.18 multiplayer. i took caffeine pills and the caffeine crash side effect was stuck on my character indefinitely. it would tick down to 1.9hrs remaining and then straight back up to 2.0hrs remaining right after</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1147,6 +1156,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1168,7 +1190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1226,6 +1248,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1235,7 +1258,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2321,20 +2345,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2343,18 +2367,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2363,18 +2387,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -2383,18 +2407,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -2403,78 +2427,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -2708,61 +2732,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="29" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="28"/>
+      <c r="B33" s="29"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="28"/>
+      <c r="B34" s="29"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="28"/>
+      <c r="B35" s="29"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="28"/>
+      <c r="B36" s="29"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="28"/>
+      <c r="B37" s="29"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="28"/>
+      <c r="B38" s="29"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="28"/>
+      <c r="B39" s="29"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="28"/>
+      <c r="B40" s="29"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="28"/>
+      <c r="B41" s="29"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -2798,33 +2822,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="30" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="29"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="29"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="29"/>
+      <c r="B6" s="30"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="29"/>
+      <c r="B7" s="30"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="29"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="29"/>
+      <c r="B9" s="30"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -2925,6 +2949,9 @@
         <v>209</v>
       </c>
       <c r="G2" s="3"/>
+      <c r="P2" s="3" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="3" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
@@ -2937,7 +2964,10 @@
         <v>208</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="Y4" s="30" t="s">
+      <c r="P4" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y4" s="31" t="s">
         <v>210</v>
       </c>
     </row>
@@ -2964,7 +2994,7 @@
       <c r="G7" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="3" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2972,7 +3002,7 @@
       <c r="B8" t="s">
         <v>199</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="3" t="s">
         <v>213</v>
       </c>
     </row>
@@ -2989,6 +3019,9 @@
         <v>201</v>
       </c>
       <c r="H10" s="3"/>
+      <c r="P10" s="27" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FD016E-9849-429C-9ABE-106BB24D036F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953F6AC0-0938-43BB-BC82-67261BC51DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="227">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1010,6 +1010,36 @@
   </si>
   <si>
     <t>i think i found a bug in b42.18 multiplayer. i took caffeine pills and the caffeine crash side effect was stuck on my character indefinitely. it would tick down to 1.9hrs remaining and then straight back up to 2.0hrs remaining right after</t>
+  </si>
+  <si>
+    <t>мп</t>
+  </si>
+  <si>
+    <t>так же судя по всему сайд эффекты рефрешаться сами по себе</t>
+  </si>
+  <si>
+    <t>комбат стимулянты не дает баф</t>
+  </si>
+  <si>
+    <t>вернее есть musle strain,в боди статус и ванильной панельке, но  мудлы не показываются</t>
+  </si>
+  <si>
+    <t xml:space="preserve">и дебаф от caffein crash </t>
+  </si>
+  <si>
+    <t>дает усталость в мп, которую никак не скинуть</t>
+  </si>
+  <si>
+    <t>дебаг меню не скидывает сайд эффекты в мп</t>
+  </si>
+  <si>
+    <t>nitrix boosters дают сайд эффект, но не дают саму боль персонажу</t>
+  </si>
+  <si>
+    <t>мп!!!!</t>
+  </si>
+  <si>
+    <t>hp loss during heat exposure</t>
   </si>
 </sst>
 </file>
@@ -2938,14 +2968,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="B2:Y61"/>
+  <dimension ref="B2:AC61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B2" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="3" t="s">
         <v>209</v>
       </c>
       <c r="G2" s="3"/>
@@ -2953,13 +2983,13 @@
         <v>215</v>
       </c>
     </row>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
         <v>207</v>
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
         <v>208</v>
       </c>
@@ -2971,7 +3001,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B5" s="22" t="s">
         <v>196</v>
       </c>
@@ -2979,7 +3009,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B6" s="22" t="s">
         <v>197</v>
       </c>
@@ -2987,7 +3017,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>198</v>
       </c>
@@ -2998,7 +3028,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>199</v>
       </c>
@@ -3006,7 +3036,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>200</v>
       </c>
@@ -3014,7 +3044,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>201</v>
       </c>
@@ -3023,22 +3053,31 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="O12" t="s">
+        <v>217</v>
+      </c>
+      <c r="P12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>205</v>
       </c>
@@ -3046,7 +3085,18 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="P15" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>219</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>206</v>
       </c>
@@ -3058,6 +3108,17 @@
       <c r="K17" s="21" t="s">
         <v>76</v>
       </c>
+      <c r="P17" t="s">
+        <v>221</v>
+      </c>
+      <c r="S17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="P19" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="20" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
@@ -3065,7 +3126,7 @@
       </c>
     </row>
     <row r="21" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="23" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3076,6 +3137,9 @@
       <c r="C23" s="10"/>
       <c r="K23" s="3" t="s">
         <v>185</v>
+      </c>
+      <c r="W23" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953F6AC0-0938-43BB-BC82-67261BC51DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCA803-FA75-4CCA-9DEF-19521AC4938F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="222">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -973,9 +973,6 @@
     <t>пациент зеро нету</t>
   </si>
   <si>
-    <t>питье с параши не дает болезнь</t>
-  </si>
-  <si>
     <t>cadeveric  без кашля</t>
   </si>
   <si>
@@ -991,9 +988,6 @@
     <t>Добавить в мод оптион чтобы открывалась либо в компакт моде либо сразу в расширенном</t>
   </si>
   <si>
-    <t>there is a small bug that i got right away , if you use quick shower from lifestyle mod it doesnt end it just keeps going</t>
-  </si>
-  <si>
     <t>antibodies panel to her</t>
   </si>
   <si>
@@ -1003,43 +997,34 @@
     <t>Вытащить стекло и раны у меня рана зажившая, у игрока без изменений</t>
   </si>
   <si>
-    <t>Common cold от купания в ванной</t>
-  </si>
-  <si>
-    <t>overload when sitting health bug</t>
-  </si>
-  <si>
-    <t>i think i found a bug in b42.18 multiplayer. i took caffeine pills and the caffeine crash side effect was stuck on my character indefinitely. it would tick down to 1.9hrs remaining and then straight back up to 2.0hrs remaining right after</t>
-  </si>
-  <si>
     <t>мп</t>
   </si>
   <si>
-    <t>так же судя по всему сайд эффекты рефрешаться сами по себе</t>
-  </si>
-  <si>
-    <t>комбат стимулянты не дает баф</t>
-  </si>
-  <si>
-    <t>вернее есть musle strain,в боди статус и ванильной панельке, но  мудлы не показываются</t>
-  </si>
-  <si>
-    <t xml:space="preserve">и дебаф от caffein crash </t>
-  </si>
-  <si>
-    <t>дает усталость в мп, которую никак не скинуть</t>
-  </si>
-  <si>
-    <t>дебаг меню не скидывает сайд эффекты в мп</t>
-  </si>
-  <si>
-    <t>nitrix boosters дают сайд эффект, но не дают саму боль персонажу</t>
-  </si>
-  <si>
-    <t>мп!!!!</t>
-  </si>
-  <si>
     <t>hp loss during heat exposure</t>
+  </si>
+  <si>
+    <t>Dangerous combos with medicine</t>
+  </si>
+  <si>
+    <t>Injection Mini-game</t>
+  </si>
+  <si>
+    <t>Panic Control / Breathing Mini-game</t>
+  </si>
+  <si>
+    <t>расинхрон по хп</t>
+  </si>
+  <si>
+    <t>после наложения можно еще раз наложить бинт или шов</t>
+  </si>
+  <si>
+    <t>можно наложить шов или бинт но после не обновляется body status, н</t>
+  </si>
+  <si>
+    <t>если держать контекстное меню активной то оно само исчезает</t>
+  </si>
+  <si>
+    <t>Making a hefty bowl of stew has given me a stage 3 concussion. Might want to tone back the circular nature of this condition. Imo.</t>
   </si>
 </sst>
 </file>
@@ -1279,6 +1264,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1288,8 +1275,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2375,20 +2360,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2397,18 +2382,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2417,18 +2402,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -2437,18 +2422,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -2457,78 +2442,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="28"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -2762,61 +2747,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="29"/>
+      <c r="B33" s="31"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="29"/>
+      <c r="B34" s="31"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="29"/>
+      <c r="B35" s="31"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="29"/>
+      <c r="B36" s="31"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="29"/>
+      <c r="B37" s="31"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="29"/>
+      <c r="B38" s="31"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="29"/>
+      <c r="B39" s="31"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="29"/>
+      <c r="B40" s="31"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="29"/>
+      <c r="B41" s="31"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -2852,33 +2837,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="32" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="30"/>
+      <c r="B4" s="32"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="30"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="30"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="30"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="30"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="30"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -2968,48 +2953,45 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="B2:AC61"/>
+  <dimension ref="B2:AB61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B2" s="25" t="s">
         <v>195</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G2" s="3"/>
-      <c r="P2" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="P3" s="27" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>208</v>
-      </c>
       <c r="C4" s="3"/>
-      <c r="P4" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y4" s="31" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="P4" s="29"/>
+      <c r="Y4" s="28"/>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B5" s="22" t="s">
         <v>196</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B6" s="22" t="s">
         <v>197</v>
       </c>
@@ -3017,7 +2999,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>198</v>
       </c>
@@ -3025,18 +3007,18 @@
         <v>63</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>199</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>200</v>
       </c>
@@ -3044,105 +3026,100 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>201</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="P10" s="27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="P10" s="27"/>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
         <v>203</v>
       </c>
       <c r="O12" t="s">
-        <v>217</v>
-      </c>
-      <c r="P12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="P13" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>205</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="P15" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y15" t="s">
+    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="AB15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB16" t="s">
         <v>219</v>
       </c>
-      <c r="AC15" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="P17" t="s">
-        <v>221</v>
-      </c>
-      <c r="S17" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="P19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="AB17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="Q18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="Q19" t="s">
+        <v>215</v>
+      </c>
+      <c r="V19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="Q20" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C21" s="23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C22" s="10"/>
     </row>
-    <row r="23" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C23" s="10"/>
       <c r="K23" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="W23" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C24" s="10" t="s">
         <v>65</v>
       </c>
@@ -3150,27 +3127,27 @@
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C25" s="10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C26" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C27" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C29" s="26" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C31" s="23" t="s">
         <v>73</v>
       </c>
@@ -3181,7 +3158,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:28" x14ac:dyDescent="0.25">
       <c r="N32" s="3" t="s">
         <v>194</v>
       </c>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCA803-FA75-4CCA-9DEF-19521AC4938F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCDEFAB-2978-4B1A-B080-E9090A78140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1000,9 +1000,6 @@
     <t>мп</t>
   </si>
   <si>
-    <t>hp loss during heat exposure</t>
-  </si>
-  <si>
     <t>Dangerous combos with medicine</t>
   </si>
   <si>
@@ -1025,6 +1022,9 @@
   </si>
   <si>
     <t>Making a hefty bowl of stew has given me a stage 3 concussion. Might want to tone back the circular nature of this condition. Imo.</t>
+  </si>
+  <si>
+    <t>чекнуть все панельки в мп и соло</t>
   </si>
 </sst>
 </file>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C3" s="3"/>
       <c r="P3" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="2:28" x14ac:dyDescent="0.25">
@@ -3045,9 +3045,10 @@
       <c r="O12" t="s">
         <v>212</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>213</v>
-      </c>
+      <c r="R12" t="s">
+        <v>221</v>
+      </c>
+      <c r="W12" s="3"/>
     </row>
     <row r="13" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
@@ -3062,7 +3063,7 @@
     </row>
     <row r="15" spans="2:28" x14ac:dyDescent="0.25">
       <c r="AB15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="2:28" x14ac:dyDescent="0.25">
@@ -3070,7 +3071,7 @@
         <v>205</v>
       </c>
       <c r="AB16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="3:28" x14ac:dyDescent="0.25">
@@ -3081,20 +3082,20 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
       <c r="Q18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="3:28" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="V19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
@@ -3102,7 +3103,7 @@
         <v>69</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCDEFAB-2978-4B1A-B080-E9090A78140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889DFE2C-B2FA-4188-9DED-4F77727AADDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="217">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -985,18 +985,6 @@
     <t>Добавить мед журнал insomnia</t>
   </si>
   <si>
-    <t>Добавить в мод оптион чтобы открывалась либо в компакт моде либо сразу в расширенном</t>
-  </si>
-  <si>
-    <t>antibodies panel to her</t>
-  </si>
-  <si>
-    <t>Панелька закрывается у другого игрока нельзя зашить</t>
-  </si>
-  <si>
-    <t>Вытащить стекло и раны у меня рана зажившая, у игрока без изменений</t>
-  </si>
-  <si>
     <t>мп</t>
   </si>
   <si>
@@ -1021,10 +1009,7 @@
     <t>если держать контекстное меню активной то оно само исчезает</t>
   </si>
   <si>
-    <t>Making a hefty bowl of stew has given me a stage 3 concussion. Might want to tone back the circular nature of this condition. Imo.</t>
-  </si>
-  <si>
-    <t>чекнуть все панельки в мп и соло</t>
+    <t>словил common cold не по тригеру</t>
   </si>
 </sst>
 </file>
@@ -2960,9 +2945,7 @@
       <c r="B2" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>208</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="G2" s="3"/>
       <c r="P2" s="3"/>
     </row>
@@ -2972,7 +2955,7 @@
       </c>
       <c r="C3" s="3"/>
       <c r="P3" s="27" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="2:28" x14ac:dyDescent="0.25">
@@ -2987,9 +2970,7 @@
       <c r="B5" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="Y5" s="3" t="s">
-        <v>209</v>
-      </c>
+      <c r="Y5" s="3"/>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B6" s="22" t="s">
@@ -3006,17 +2987,13 @@
       <c r="G7" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>210</v>
-      </c>
+      <c r="P7" s="3"/>
     </row>
     <row r="8" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>199</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="P8" s="3"/>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
@@ -3043,10 +3020,7 @@
         <v>203</v>
       </c>
       <c r="O12" t="s">
-        <v>212</v>
-      </c>
-      <c r="R12" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="W12" s="3"/>
     </row>
@@ -3063,7 +3037,7 @@
     </row>
     <row r="15" spans="2:28" x14ac:dyDescent="0.25">
       <c r="AB15" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="2:28" x14ac:dyDescent="0.25">
@@ -3071,7 +3045,7 @@
         <v>205</v>
       </c>
       <c r="AB16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="3:28" x14ac:dyDescent="0.25">
@@ -3082,20 +3056,20 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.25">
       <c r="Q18" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="3:28" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="V19" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
@@ -3103,7 +3077,7 @@
         <v>69</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889DFE2C-B2FA-4188-9DED-4F77727AADDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962CA879-B023-4B6E-8972-0AF218D4EF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="219">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1010,6 +1010,12 @@
   </si>
   <si>
     <t>словил common cold не по тригеру</t>
+  </si>
+  <si>
+    <t>Сделать мод на кальян</t>
+  </si>
+  <si>
+    <t>Сделать мод на рубку деревьев</t>
   </si>
 </sst>
 </file>
@@ -2948,6 +2954,9 @@
       <c r="E2" s="3"/>
       <c r="G2" s="3"/>
       <c r="P2" s="3"/>
+      <c r="U2" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
@@ -2956,6 +2965,9 @@
       <c r="C3" s="3"/>
       <c r="P3" s="27" t="s">
         <v>216</v>
+      </c>
+      <c r="U3" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="2:28" x14ac:dyDescent="0.25">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962CA879-B023-4B6E-8972-0AF218D4EF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838174D7-2B69-417F-9D03-5116BA0665AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="Environmental " sheetId="7" r:id="rId4"/>
     <sheet name="Blood" sheetId="8" r:id="rId5"/>
     <sheet name="Не забыть" sheetId="5" r:id="rId6"/>
-    <sheet name="RadioDialogues" sheetId="9" r:id="rId7"/>
-    <sheet name="Mechanics" sheetId="3" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId7"/>
+    <sheet name="RadioDialogues" sheetId="9" r:id="rId8"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="223">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1017,12 +1018,24 @@
   <si>
     <t>Сделать мод на рубку деревьев</t>
   </si>
+  <si>
+    <t>chamomile</t>
+  </si>
+  <si>
+    <t>marigold</t>
+  </si>
+  <si>
+    <t>plantain</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1175,6 +1188,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1196,7 +1214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1266,6 +1284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3257,6 +3276,34 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7944FC-5C7A-4B02-B021-398DF4A45490}">
+  <dimension ref="C3:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A4C555-5941-44D5-8766-80774E93DFFB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3268,7 +3315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
   <dimension ref="B3:Z42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B69A50-14E4-48AD-8882-6041FC80AD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838174D7-2B69-417F-9D03-5116BA0665AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="3180" windowWidth="28800" windowHeight="14355" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="Environmental " sheetId="7" r:id="rId4"/>
     <sheet name="Blood" sheetId="8" r:id="rId5"/>
     <sheet name="Не забыть" sheetId="5" r:id="rId6"/>
-    <sheet name="RadioDialogues" sheetId="9" r:id="rId7"/>
-    <sheet name="Mechanics" sheetId="3" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId7"/>
+    <sheet name="RadioDialogues" sheetId="9" r:id="rId8"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="223">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -946,14 +947,95 @@
     <t>Доделать Cellulitis</t>
   </si>
   <si>
-    <t>Add loot to gigamart</t>
+    <t>Funriture rest bonus</t>
+  </si>
+  <si>
+    <t>1. Медицна не дает болзень смотетьб</t>
+  </si>
+  <si>
+    <t>2. Шизу слышна всем</t>
+  </si>
+  <si>
+    <t>3. Медикаменты не показываются</t>
+  </si>
+  <si>
+    <t>4 не апдейтися сразу</t>
+  </si>
+  <si>
+    <t>5. Тетанус не прокает</t>
+  </si>
+  <si>
+    <t>6. Кровь очень медленно снижается</t>
+  </si>
+  <si>
+    <t>7 Странно синхронизируется травмы</t>
+  </si>
+  <si>
+    <t>пациент зеро нету</t>
+  </si>
+  <si>
+    <t>cadeveric  без кашля</t>
+  </si>
+  <si>
+    <t>Сместился курсор</t>
+  </si>
+  <si>
+    <t>Defibrilator?</t>
+  </si>
+  <si>
+    <t>Добавить мед журнал insomnia</t>
+  </si>
+  <si>
+    <t>мп</t>
+  </si>
+  <si>
+    <t>Dangerous combos with medicine</t>
+  </si>
+  <si>
+    <t>Injection Mini-game</t>
+  </si>
+  <si>
+    <t>Panic Control / Breathing Mini-game</t>
+  </si>
+  <si>
+    <t>расинхрон по хп</t>
+  </si>
+  <si>
+    <t>после наложения можно еще раз наложить бинт или шов</t>
+  </si>
+  <si>
+    <t>можно наложить шов или бинт но после не обновляется body status, н</t>
+  </si>
+  <si>
+    <t>если держать контекстное меню активной то оно само исчезает</t>
+  </si>
+  <si>
+    <t>словил common cold не по тригеру</t>
+  </si>
+  <si>
+    <t>Сделать мод на кальян</t>
+  </si>
+  <si>
+    <t>Сделать мод на рубку деревьев</t>
+  </si>
+  <si>
+    <t>chamomile</t>
+  </si>
+  <si>
+    <t>marigold</t>
+  </si>
+  <si>
+    <t>plantain</t>
+  </si>
+  <si>
+    <t>add</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1081,6 +1163,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1102,7 +1214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1151,6 +1263,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1160,12 +1284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1628,55 +1747,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>29479</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>162521</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FCA23F4-7683-2C80-A33A-734BF96A886E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8181975" y="171450"/>
-          <a:ext cx="6477904" cy="4267796"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2300,20 +2370,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2322,18 +2392,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2342,18 +2412,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -2362,18 +2432,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -2382,78 +2452,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -2687,61 +2757,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="31" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="23"/>
+      <c r="B33" s="31"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="23"/>
+      <c r="B34" s="31"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="23"/>
+      <c r="B35" s="31"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="23"/>
+      <c r="B36" s="31"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="23"/>
+      <c r="B37" s="31"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="23"/>
+      <c r="B38" s="31"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="23"/>
+      <c r="B39" s="31"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="23"/>
+      <c r="B40" s="31"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="23"/>
+      <c r="B41" s="31"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -2777,33 +2847,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="32" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="24"/>
+      <c r="B4" s="32"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="24"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="24"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="24"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="24"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="24"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -2893,112 +2963,208 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
-  <dimension ref="B2:W61"/>
+  <dimension ref="B2:AB61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G2" s="3" t="s">
+    <row r="2" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B2" s="25" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="U2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B3" s="25" t="s">
+        <v>206</v>
+      </c>
       <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="P3" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="U3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>207</v>
+      </c>
       <c r="C4" s="3"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="P4" s="29"/>
+      <c r="Y4" s="28"/>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y5" s="3"/>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="22" t="s">
+        <v>197</v>
+      </c>
       <c r="G6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G7" s="28" t="s">
+    <row r="7" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" s="25" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
+      <c r="P7" s="3"/>
+    </row>
+    <row r="8" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>199</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="H10" s="3"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="P10" s="27"/>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B12" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="O12" t="s">
+        <v>208</v>
+      </c>
+      <c r="W12" s="3"/>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="I14" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="AB15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K17" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="Q18" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.25">
+      <c r="Q19" t="s">
+        <v>210</v>
+      </c>
+      <c r="V19" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="20" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C20" s="10" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C21" s="10" t="s">
+      <c r="Q20" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C21" s="23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C22" s="10"/>
     </row>
-    <row r="23" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C23" s="10"/>
       <c r="K23" s="3" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="24" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C24" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" s="21" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C25" s="10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C26" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C27" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
       <c r="C29" s="26" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="3:23" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="C31" s="26" t="s">
+    <row r="31" spans="3:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C31" s="23" t="s">
         <v>73</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="N31" s="27" t="s">
+      <c r="N31" s="24" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:28" x14ac:dyDescent="0.25">
       <c r="N32" s="3" t="s">
         <v>194</v>
       </c>
@@ -3027,7 +3193,7 @@
     </row>
     <row r="36" spans="3:23" x14ac:dyDescent="0.25">
       <c r="I36" s="3"/>
-      <c r="L36" s="3" t="s">
+      <c r="L36" s="21" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3035,7 +3201,7 @@
       <c r="K39" s="3"/>
     </row>
     <row r="41" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="K41" s="27" t="s">
+      <c r="K41" s="24" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3045,11 +3211,11 @@
       </c>
     </row>
     <row r="43" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="21" t="s">
         <v>147</v>
       </c>
       <c r="F43" s="3"/>
-      <c r="K43" s="27" t="s">
+      <c r="K43" s="24" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3066,7 +3232,7 @@
       <c r="R46" s="3"/>
     </row>
     <row r="47" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="21" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3106,11 +3272,38 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7944FC-5C7A-4B02-B021-398DF4A45490}">
+  <dimension ref="C3:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A4C555-5941-44D5-8766-80774E93DFFB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3122,7 +3315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
   <dimension ref="B3:Z42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3132,260 +3325,260 @@
   <sheetData>
     <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C3" s="3"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
     </row>
     <row r="4" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25" t="s">
+      <c r="M4" s="22"/>
+      <c r="N4" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="O4" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
     </row>
     <row r="5" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25" t="s">
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
     </row>
     <row r="6" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B6" s="7"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25" t="s">
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="25"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="25"/>
-      <c r="X6" s="25"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
     </row>
     <row r="7" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B7" s="7"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25" t="s">
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="25"/>
-      <c r="V7" s="25"/>
-      <c r="W7" s="25"/>
-      <c r="X7" s="25"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
     </row>
     <row r="8" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B8" s="7"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25" t="s">
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="25"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
     </row>
     <row r="9" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B9" s="8"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25" t="s">
+      <c r="M9" s="22"/>
+      <c r="N9" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="O9" s="25" t="s">
+      <c r="O9" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
     </row>
     <row r="10" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B10" s="8"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25" t="s">
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="25"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
     </row>
     <row r="11" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B11" s="7"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25" t="s">
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
     </row>
     <row r="12" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B12" s="7"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25" t="s">
+      <c r="M12" s="22"/>
+      <c r="N12" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="O12" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25" t="s">
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-      <c r="X12" s="25"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
     </row>
     <row r="13" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B13" s="7"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25" t="s">
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25" t="s">
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="25"/>
-      <c r="X13" s="25"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
     </row>
     <row r="14" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B14" s="7"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25" t="s">
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-      <c r="X14" s="25"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
     </row>
     <row r="15" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B15" s="7"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
     </row>
     <row r="16" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
-      <c r="S16" s="25"/>
-      <c r="T16" s="25"/>
-      <c r="U16" s="25"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="25"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
@@ -3491,14 +3684,14 @@
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H36" s="25" t="s">
+      <c r="H36" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25" t="s">
+      <c r="I36" s="22"/>
+      <c r="J36" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="K36" s="25"/>
+      <c r="K36" s="22"/>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.25">
       <c r="H38" t="s">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838174D7-2B69-417F-9D03-5116BA0665AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1D05C4-B1C8-41FE-99FA-DE50EC76CCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="254">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1029,6 +1029,99 @@
   </si>
   <si>
     <t>add</t>
+  </si>
+  <si>
+    <t>spiderweb</t>
+  </si>
+  <si>
+    <t>trees</t>
+  </si>
+  <si>
+    <t>bushes</t>
+  </si>
+  <si>
+    <t>berries?</t>
+  </si>
+  <si>
+    <t>beef</t>
+  </si>
+  <si>
+    <t>mutton chop</t>
+  </si>
+  <si>
+    <t>Reciepe=beef+water pot (if possible cook it)</t>
+  </si>
+  <si>
+    <t>Reciepe=mutton chop+water pot (if possible cook it)</t>
+  </si>
+  <si>
+    <t>Adrenaline Injections</t>
+  </si>
+  <si>
+    <t>black sage</t>
+  </si>
+  <si>
+    <t>comfrey</t>
+  </si>
+  <si>
+    <t>common mallow</t>
+  </si>
+  <si>
+    <t>ginseng</t>
+  </si>
+  <si>
+    <t>(no dired)</t>
+  </si>
+  <si>
+    <t>Wild garlic</t>
+  </si>
+  <si>
+    <t>(dired)</t>
+  </si>
+  <si>
+    <t>spiderweb bandage</t>
+  </si>
+  <si>
+    <t>honey comb</t>
+  </si>
+  <si>
+    <t>tallow/lard</t>
+  </si>
+  <si>
+    <t>Homemade muscle relaxant=2 black sage, 1 chamomile, 1 comfrey, 1 honey, mortar and pestle</t>
+  </si>
+  <si>
+    <t>Homemade cough syrup=clean water bottle,1 honey, 2 common mallow, 1 chamomile, 1 berries ,mortar and pestle</t>
+  </si>
+  <si>
+    <t>Homemade topical permetrin=4 marigold, 1 alchoholic wipes/bottle of disinficant/rubbing alchohol, 1 wild garlic, 1 honey, mortar and pestle</t>
+  </si>
+  <si>
+    <t>Herbal tea (1 use) (Common Cold Cure)= 1 cup of water, 1 chamomile, 1 berries, 1 honey</t>
+  </si>
+  <si>
+    <t>Homemade antiphyretic tea (1 use) = 1 cup of water, 2 lemongras, 1 chamomile, 1 lavender</t>
+  </si>
+  <si>
+    <t>Homemade painkillers= 5 black sage, 3 chamomile, mortar and pestle</t>
+  </si>
+  <si>
+    <t>Homemade Antiseptic Cream=1 tallow/lard, 1 honey,1 wild garlic (garlic) 3 plantain, mortar and pestle</t>
+  </si>
+  <si>
+    <t>Homemade Antibiotic Oitment=1 tallow/lard, 1 honey, 1 lavender, 3 wild garlic(garlic) 2 plantain, 3 comfrey, mortart and pestle</t>
+  </si>
+  <si>
+    <t>Homemade sleeping Pills= 3 chamomile, 1 black sage, 1 honey, mortar and pestle</t>
+  </si>
+  <si>
+    <t>Homemade Relaxing Tea (1 use) (decreases stress)=1 cup of water, 2 chamomile, 3 lavender, 1 common mallow, 1 berries, mortar and pestle</t>
+  </si>
+  <si>
+    <t>chamomile, marigold, plantain, berries,black sage, comfrey, common mallow, ginseng, Wild garlic, lavander</t>
+  </si>
+  <si>
+    <t>Sellulitis can progress to sepsis?</t>
   </si>
 </sst>
 </file>
@@ -3010,6 +3103,9 @@
       <c r="G6" t="s">
         <v>74</v>
       </c>
+      <c r="P6" s="3" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -3277,25 +3373,156 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7944FC-5C7A-4B02-B021-398DF4A45490}">
-  <dimension ref="C3:D5"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="75.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K1" t="s">
+        <v>224</v>
+      </c>
+      <c r="N1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K3" t="s">
+        <v>240</v>
+      </c>
+      <c r="N3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>222</v>
-      </c>
+      <c r="K4" t="s">
+        <v>223</v>
+      </c>
+      <c r="N4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D5" s="33" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>226</v>
+      </c>
+      <c r="N6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="N7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>233</v>
+      </c>
+      <c r="T11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="19" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L19" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L22" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L24" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1D05C4-B1C8-41FE-99FA-DE50EC76CCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF37127F-93B5-40D9-8120-BDEFF90D9F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="255">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1122,6 +1122,9 @@
   </si>
   <si>
     <t>Sellulitis can progress to sepsis?</t>
+  </si>
+  <si>
+    <t>словил кнокс в мультиплеере с царапины при кусте</t>
   </si>
 </sst>
 </file>
@@ -3438,6 +3441,11 @@
         <v>230</v>
       </c>
     </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>254</v>
+      </c>
+    </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>232</v>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF37127F-93B5-40D9-8120-BDEFF90D9F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F18054-644F-4B60-889B-9EE860CEEF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="258">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1049,12 +1049,6 @@
     <t>mutton chop</t>
   </si>
   <si>
-    <t>Reciepe=beef+water pot (if possible cook it)</t>
-  </si>
-  <si>
-    <t>Reciepe=mutton chop+water pot (if possible cook it)</t>
-  </si>
-  <si>
     <t>Adrenaline Injections</t>
   </si>
   <si>
@@ -1124,7 +1118,22 @@
     <t>Sellulitis can progress to sepsis?</t>
   </si>
   <si>
-    <t>словил кнокс в мультиплеере с царапины при кусте</t>
+    <t>Spiderweb bandage=3 Spiderweb</t>
+  </si>
+  <si>
+    <t>Suturing needle=1 Spiderweb+1 any needle</t>
+  </si>
+  <si>
+    <t>Prepare Tallow=1beef+water pot (if possible cook it)</t>
+  </si>
+  <si>
+    <t>Prepare tallow=1mutton chop+water pot (if possible cook it)</t>
+  </si>
+  <si>
+    <t>Honey=1 Honecomb + stone hammer or wooden mallet or ham? Hammer or mortar and pestle</t>
+  </si>
+  <si>
+    <t>отменить перчатки для honey</t>
   </si>
 </sst>
 </file>
@@ -1371,6 +1380,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1380,7 +1390,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2466,20 +2475,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2488,18 +2497,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2508,18 +2517,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -2528,18 +2537,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -2548,78 +2557,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -2853,61 +2862,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="31"/>
+      <c r="B33" s="32"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="31"/>
+      <c r="B34" s="32"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="31"/>
+      <c r="B35" s="32"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="31"/>
+      <c r="B36" s="32"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="31"/>
+      <c r="B37" s="32"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="31"/>
+      <c r="B38" s="32"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="31"/>
+      <c r="B39" s="32"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="31"/>
+      <c r="B40" s="32"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="31"/>
+      <c r="B41" s="32"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -2943,33 +2952,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="32"/>
+      <c r="B4" s="33"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="32"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="32"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -3107,7 +3116,7 @@
         <v>74</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.25">
@@ -3376,7 +3385,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7944FC-5C7A-4B02-B021-398DF4A45490}">
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="75.85546875" customWidth="1"/>
@@ -3390,12 +3399,12 @@
         <v>224</v>
       </c>
       <c r="N1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -3406,7 +3415,7 @@
         <v>222</v>
       </c>
       <c r="K3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N3" t="s">
         <v>227</v>
@@ -3424,7 +3433,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="30" t="s">
         <v>221</v>
       </c>
     </row>
@@ -3432,105 +3441,118 @@
       <c r="D6" t="s">
         <v>226</v>
       </c>
+      <c r="L6" t="s">
+        <v>256</v>
+      </c>
       <c r="N6" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L8" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L9" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="T11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="L15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="L16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L24" t="s">
-        <v>251</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L26" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="27" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L27" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F18054-644F-4B60-889B-9EE860CEEF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4295C1EA-0A2D-4832-BB62-3E9472359C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="259">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1134,6 +1134,9 @@
   </si>
   <si>
     <t>отменить перчатки для honey</t>
+  </si>
+  <si>
+    <t>Spiderweb bandage=1 rag, 10 spider web</t>
   </si>
 </sst>
 </file>
@@ -3475,6 +3478,9 @@
       <c r="D12" t="s">
         <v>232</v>
       </c>
+      <c r="L12" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D13" t="s">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4295C1EA-0A2D-4832-BB62-3E9472359C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C247C9-9F6D-4CB0-B962-2C20C3491653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="259">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -3465,6 +3465,9 @@
       <c r="D10" t="s">
         <v>230</v>
       </c>
+      <c r="L10" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D11" t="s">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C247C9-9F6D-4CB0-B962-2C20C3491653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4282C768-28C4-4986-B81C-36471C6FDD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17130" yWindow="2940" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,9 @@
     <sheet name="Blood" sheetId="8" r:id="rId5"/>
     <sheet name="Не забыть" sheetId="5" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="10" r:id="rId7"/>
-    <sheet name="RadioDialogues" sheetId="9" r:id="rId8"/>
-    <sheet name="Mechanics" sheetId="3" r:id="rId9"/>
+    <sheet name="Bugs" sheetId="11" r:id="rId8"/>
+    <sheet name="RadioDialogues" sheetId="9" r:id="rId9"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="273">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1138,12 +1139,54 @@
   <si>
     <t>Spiderweb bandage=1 rag, 10 spider web</t>
   </si>
+  <si>
+    <t>Не проигрывается звук чихания при фаст форварде при простуде</t>
+  </si>
+  <si>
+    <t>Проверить температуру как работает!!!</t>
+  </si>
+  <si>
+    <t>Some medications disappear when consolidate them with this mod installed I noticed this mostly with sleeping pills</t>
+  </si>
+  <si>
+    <t>when an injury heals on your character and you remove the bandage other players on MP will still see the bandage from their side</t>
+  </si>
+  <si>
+    <t>when you take medication for one of the new illnesses after you are done with the medication you still won’t get healed</t>
+  </si>
+  <si>
+    <t>the minigames like stitching needs a scaling fix</t>
+  </si>
+  <si>
+    <t>there’s some issues with food borne illnesses from non vanilla foods like vanilla foods expanded</t>
+  </si>
+  <si>
+    <t>you should add diabetes as negative trait or maybe some other diseases that are permanent as traits</t>
+  </si>
+  <si>
+    <t>Any idea why meditating (from lifestyle) produces heat?</t>
+  </si>
+  <si>
+    <t>Infection from canned food</t>
+  </si>
+  <si>
+    <t>inspecting health for other characters shows side effects multiplied infinitely, for instance mild nausea on my GFs health tab shows maybe 200 times and it keeps refreshing.</t>
+  </si>
+  <si>
+    <t> On my server, I’m using a cold environment, so I set the ambient temperature down to -20°C. The problem is that it locks my body temperature at 35.9°C no matter what I do. Even if I run in place continuously or stand right next to a fire, I can’t fully escape the hypothermia. I tried lowering the disease stage to the lowest level (stage 1 at 31°C), but I still get stuck with hypothermia at 35°C. When I turn off body temperature entirely, everything returns to normal.</t>
+  </si>
+  <si>
+    <t>Im playing on a multiplayer server without any other medical rework mods and im playing as the EHR doctor for the journal knowladge of dieseases and it seems my doc gets amnesia cause after about 5 minutes of playing i lose knowladge about all the dieseases and theres no errors to it</t>
+  </si>
+  <si>
+    <t>изменить pneumonia chance на 35%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1301,6 +1344,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF7030A0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1322,7 +1383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1391,6 +1452,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2272,6 +2338,404 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
+  <dimension ref="B3:Z42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C3" s="3"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+    </row>
+    <row r="4" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B4" s="8"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="O4" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+    </row>
+    <row r="5" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="7"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+    </row>
+    <row r="6" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="7"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+    </row>
+    <row r="7" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="7"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="22"/>
+    </row>
+    <row r="8" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="7"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+    </row>
+    <row r="9" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="8"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="O9" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+    </row>
+    <row r="10" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="8"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="22"/>
+    </row>
+    <row r="11" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="7"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+    </row>
+    <row r="12" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="7"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="O12" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
+    </row>
+    <row r="13" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="7"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+    </row>
+    <row r="14" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="7"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+    </row>
+    <row r="15" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="7"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+    </row>
+    <row r="16" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="8"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B17" s="9"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B18" s="9"/>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B20" s="9"/>
+    </row>
+    <row r="21" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="7"/>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" t="s">
+        <v>168</v>
+      </c>
+      <c r="L22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>165</v>
+      </c>
+      <c r="F24" t="s">
+        <v>166</v>
+      </c>
+      <c r="L24" t="s">
+        <v>163</v>
+      </c>
+      <c r="N24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="S26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="S27" t="s">
+        <v>192</v>
+      </c>
+      <c r="X27" s="3"/>
+      <c r="Z27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="H28" t="s">
+        <v>149</v>
+      </c>
+      <c r="S28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="S29" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="H30" t="s">
+        <v>150</v>
+      </c>
+      <c r="J30" t="s">
+        <v>151</v>
+      </c>
+      <c r="S30" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="H32" t="s">
+        <v>152</v>
+      </c>
+      <c r="I32" t="s">
+        <v>153</v>
+      </c>
+      <c r="J32" t="s">
+        <v>154</v>
+      </c>
+      <c r="S32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="S33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="H34" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="H36" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="K36" s="22"/>
+    </row>
+    <row r="38" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="H38" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="H40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="8:19" x14ac:dyDescent="0.25">
+      <c r="H42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3715F01A-79F6-4956-8F11-0E2F67879F36}">
   <dimension ref="B3:U42"/>
@@ -3570,6 +4034,192 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6582FB11-E4E7-44CC-B6AC-D03433973810}">
+  <dimension ref="B2:V21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B3" s="30" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B5" s="27" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B6" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="V6" s="34" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B7" s="30" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B8" s="35" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="30" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B12" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B16" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B12:O14"/>
+    <mergeCell ref="B16:O19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A4C555-5941-44D5-8766-80774E93DFFB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3579,402 +4229,4 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
-  <dimension ref="B3:Z42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="C3" s="3"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-    </row>
-    <row r="4" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="8"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="O4" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-    </row>
-    <row r="5" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="7"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-    </row>
-    <row r="6" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="7"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-    </row>
-    <row r="7" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="7"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-    </row>
-    <row r="8" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-    </row>
-    <row r="9" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="O9" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-    </row>
-    <row r="10" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="8"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-    </row>
-    <row r="11" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="7"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-    </row>
-    <row r="12" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="7"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="O12" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-    </row>
-    <row r="13" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="7"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-    </row>
-    <row r="14" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="22"/>
-    </row>
-    <row r="15" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="7"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-    </row>
-    <row r="16" spans="2:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="22"/>
-    </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B17" s="9"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
-    </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-    </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B19" s="9"/>
-    </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B20" s="9"/>
-    </row>
-    <row r="21" spans="2:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="7"/>
-    </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" t="s">
-        <v>168</v>
-      </c>
-      <c r="L22" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>165</v>
-      </c>
-      <c r="F24" t="s">
-        <v>166</v>
-      </c>
-      <c r="L24" t="s">
-        <v>163</v>
-      </c>
-      <c r="N24" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="S26" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="S27" t="s">
-        <v>192</v>
-      </c>
-      <c r="X27" s="3"/>
-      <c r="Z27" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="H28" t="s">
-        <v>149</v>
-      </c>
-      <c r="S28" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="S29" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="H30" t="s">
-        <v>150</v>
-      </c>
-      <c r="J30" t="s">
-        <v>151</v>
-      </c>
-      <c r="S30" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="H32" t="s">
-        <v>152</v>
-      </c>
-      <c r="I32" t="s">
-        <v>153</v>
-      </c>
-      <c r="J32" t="s">
-        <v>154</v>
-      </c>
-      <c r="S32" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="S33" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="34" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H34" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H36" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="K36" s="22"/>
-    </row>
-    <row r="38" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H38" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="40" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H40" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="42" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H42" t="s">
-        <v>161</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4282C768-28C4-4986-B81C-36471C6FDD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865B0CF1-497F-46B6-B652-FE2C6DC82974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-17130" yWindow="2940" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="274">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1180,6 +1180,9 @@
   </si>
   <si>
     <t>изменить pneumonia chance на 35%</t>
+  </si>
+  <si>
+    <t>?? Врод еработает</t>
   </si>
 </sst>
 </file>
@@ -4042,6 +4045,9 @@
       <c r="B2" t="s">
         <v>259</v>
       </c>
+      <c r="I2" t="s">
+        <v>273</v>
+      </c>
       <c r="Q2" t="s">
         <v>260</v>
       </c>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865B0CF1-497F-46B6-B652-FE2C6DC82974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222FC783-F7AE-48FC-8FAD-99F075094B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17130" yWindow="2940" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="2385" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -1189,7 +1189,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1365,6 +1365,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF92D050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1386,7 +1392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1448,6 +1454,8 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1457,11 +1465,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2945,20 +2952,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2967,18 +2974,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2987,18 +2994,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -3007,18 +3014,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="33"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -3027,78 +3034,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -3332,61 +3339,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="34" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="32"/>
+      <c r="B33" s="34"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="32"/>
+      <c r="B34" s="34"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="32"/>
+      <c r="B35" s="34"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="32"/>
+      <c r="B36" s="34"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="32"/>
+      <c r="B37" s="34"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="32"/>
+      <c r="B38" s="34"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="32"/>
+      <c r="B39" s="34"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="32"/>
+      <c r="B40" s="34"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="32"/>
+      <c r="B41" s="34"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="33" t="s">
+      <c r="C42" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -3422,33 +3429,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="35" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="33"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="33"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="33"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="33"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="33"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="33"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -4053,7 +4060,7 @@
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>261</v>
       </c>
     </row>
@@ -4063,7 +4070,7 @@
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="37" t="s">
         <v>263</v>
       </c>
     </row>
@@ -4071,7 +4078,7 @@
       <c r="B6" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="V6" s="34" t="s">
+      <c r="V6" s="27" t="s">
         <v>266</v>
       </c>
     </row>
@@ -4081,7 +4088,7 @@
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="32" t="s">
         <v>267</v>
       </c>
     </row>
@@ -4146,70 +4153,70 @@
       <c r="O14" s="36"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E21" t="s">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222FC783-F7AE-48FC-8FAD-99F075094B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CACFA0-E514-47CB-8B91-8C5F95A5473B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="2385" windowWidth="33525" windowHeight="14355" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="2385" windowWidth="33525" windowHeight="14355" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="276">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1183,6 +1183,12 @@
   </si>
   <si>
     <t>?? Врод еработает</t>
+  </si>
+  <si>
+    <t>HER_Disease.lua</t>
+  </si>
+  <si>
+    <t>debugFoodPoisoning=false</t>
   </si>
 </sst>
 </file>
@@ -1456,6 +1462,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1468,7 +1475,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2952,20 +2958,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -2974,18 +2980,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -2994,18 +3000,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -3014,18 +3020,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -3034,78 +3040,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -3339,61 +3345,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="35" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="34"/>
+      <c r="B34" s="35"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="34"/>
+      <c r="B36" s="35"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="34"/>
+      <c r="B37" s="35"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="34"/>
+      <c r="B38" s="35"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="34"/>
+      <c r="B39" s="35"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="34"/>
+      <c r="B40" s="35"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="34"/>
+      <c r="B41" s="35"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="35" t="s">
+      <c r="C42" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -3429,33 +3435,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="36" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="35"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="35"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="35"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="35"/>
+      <c r="B8" s="36"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="35"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -3988,52 +3994,58 @@
         <v>247</v>
       </c>
     </row>
-    <row r="17" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L17" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="18" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L18" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>274</v>
+      </c>
       <c r="L19" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="20" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>275</v>
+      </c>
       <c r="L20" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="21" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L21" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="22" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L22" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="23" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L23" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="24" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L24" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="26" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L26" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="27" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L27" t="s">
         <v>252</v>
       </c>
@@ -4070,7 +4082,7 @@
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="33" t="s">
         <v>263</v>
       </c>
     </row>
@@ -4103,120 +4115,120 @@
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="37"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E21" t="s">

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CACFA0-E514-47CB-8B91-8C5F95A5473B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5B2376-A2E5-4CC8-B33F-1E6EED63E6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="2385" windowWidth="33525" windowHeight="14355" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1110" yWindow="6525" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId1"/>
-    <sheet name="Corpse sickness (IGDnewMechanic" sheetId="2" r:id="rId2"/>
-    <sheet name="Wound Infections" sheetId="6" r:id="rId3"/>
-    <sheet name="Environmental " sheetId="7" r:id="rId4"/>
-    <sheet name="Blood" sheetId="8" r:id="rId5"/>
-    <sheet name="Не забыть" sheetId="5" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId7"/>
-    <sheet name="Bugs" sheetId="11" r:id="rId8"/>
-    <sheet name="RadioDialogues" sheetId="9" r:id="rId9"/>
-    <sheet name="Mechanics" sheetId="3" r:id="rId10"/>
+    <sheet name="TODO" sheetId="12" r:id="rId1"/>
+    <sheet name="Food Related (I guess Done)" sheetId="1" r:id="rId2"/>
+    <sheet name="Corpse sickness (IGDnewMechanic" sheetId="2" r:id="rId3"/>
+    <sheet name="Wound Infections" sheetId="6" r:id="rId4"/>
+    <sheet name="Environmental " sheetId="7" r:id="rId5"/>
+    <sheet name="Blood" sheetId="8" r:id="rId6"/>
+    <sheet name="Не забыть" sheetId="5" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId8"/>
+    <sheet name="Bugs" sheetId="11" r:id="rId9"/>
+    <sheet name="RadioDialogues" sheetId="9" r:id="rId10"/>
+    <sheet name="Mechanics" sheetId="3" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="295">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1189,6 +1190,110 @@
   </si>
   <si>
     <t>debugFoodPoisoning=false</t>
+  </si>
+  <si>
+    <t>Progression of diseaseses keep progressing when offline</t>
+  </si>
+  <si>
+    <t>Consolidation all problems</t>
+  </si>
+  <si>
+    <t>Consolidating items such as the antibiotic ointment and cough syrup will bug out and remove the itme, but it will return after relogging.</t>
+  </si>
+  <si>
+    <t>Not sure if it's a bug or just desync hence why I'm putting it here but in multiplayer both me and my friend have different illness whenever checking him. He has gastrointeritus where as I see he has dystery, I see an infected hand whereas he doesn't. Hard to tell what is actually to worry about.</t>
+  </si>
+  <si>
+    <t>hi I found bug I think... I playing in MP with my friend. We have a doctor. I have insomnia and I can't sleep if I don't take a sleep pills, but I take it and nothing happens but when the doctor forces to me to take it it works and I can see "active mediaction" but when I take those pills "active medication" shows nothing...</t>
+  </si>
+  <si>
+    <t>Vanilla meds not work?</t>
+  </si>
+  <si>
+    <t>What exactly happened: I'm not sure what's going on, but the painkillers aren't working for me. I take the pill, the dose is consumed, but there's no sign of any effect—neither on the panel interface, nor on the icons on the right, nor any pain relief
+-What steps did you take: took the painkillers to relieve the pain; the pill bottle; took a pill
+-MP or single-player: SP. Вот этот коммент с подозрением надо посмотреть, скорее всего там все ок</t>
+  </si>
+  <si>
+    <t>When tryingn to stitch friend in self hosted multiplayer, the mini game window that opens immediately disappears</t>
+  </si>
+  <si>
+    <t>Тоже проверить действительно ли так или просто дистанция большая</t>
+  </si>
+  <si>
+    <t>MP,
+Washing hands
+[10-08-26 00:10:57.325] ERROR: General f:570474 st:34,309,308 at KahluaThread.flushErrorMessage &gt; dumping Lua stack trace
+-----------------------------------------
+STACK TRACE
+-----------------------------------------
+Lua((MOD:Extensive Health Rework Evolved B42)).update(EHR_WashHands.lua:184).
+[10-08-26 00:10:57.325] ERROR: General f:570474 st:34,309,308&gt; Lua((MOD:Extensive Health Rework Evolved B42)).update&gt; Exception thrown
+java.lang.IllegalStateException: Forward Direction cannot be zero length vector. at IsoGameCharacter.setForwardDirection(IsoGameCharacter.java:2827).
+Stack trace:
+zombie.characters.IsoGameCharacter.setForwardDirection(IsoGameCharacter.java:2827)
+zombie.characters.IsoGameCharacter.setForwardDirection(IsoGameCharacter.java:2808)
+zombie.characters.IsoGameCharacter.faceThisObjectAlt(IsoGameCharacter.java:10609)
+java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(Unknown Source)
+java.base/java.lang.reflect.Method.invoke(Unknown Source)
+se.krka.kahlua.integration.expose.caller.MethodCaller.call(MethodCaller.java:58)
+se.krka.kahlua.integration.expose.LuaJavaInvoker.call(LuaJavaInvoker.java:194)
+se.krka.kahlua.integration.expose.LuaJavaInvoker.call(LuaJavaInvoker.java:184)
+se.krka.kahlua.vm.KahluaThread.callJava(KahluaThread.java:178)
+Lua((MOD:Extensive Health Rework Evolved B42)).update(EHR_WashHands.lua:184)
+se.krka.kahlua.vm.KahluaThread.luaMainloop(KahluaThread.java:795)
+se.krka.kahlua.vm.KahluaThread.call(KahluaThread.java:162)
+se.krka.kahlua.vm.KahluaThread.pcall(KahluaThread.java:1740)
+se.krka.kahlua.vm.KahluaThread.pcallvoid(KahluaThread.java:1584)
+se.krka.kahlua.integration.LuaCaller.pcallvoid(LuaCaller.java:35)
+zombie.characters.CharacterTimedActions.LuaTimedActionNew.update(LuaTimedActionNew.java:87)
+zombie.characters.IsoGameCharacter.updateInternal(IsoGameCharacter.java:9189)
+zombie.characters.IsoGameCharacter.update(IsoGameCharacter.java:8820)
+zombie.characters.IsoPlayer.updateInternal1(IsoPlayer.java:2206)
+zombie.characters.IsoPlayer.update(IsoPlayer.java:2184)
+zombie.MovingObjectUpdateSchedulerUpdateBucket.update(MovingObjectUpdateSchedulerUpdateBucket.java:58)
+zombie.MovingObjectUpdateScheduler.update(MovingObjectUpdateScheduler.java:150)
+zombie.iso.IsoCell.ProcessObjects(IsoCell.java:2662)
+zombie.iso.IsoCell.updateInternal(IsoCell.java:4905)
+zombie.iso.IsoCell.update(IsoCell.java:4862)
+zombie.iso.IsoWorld.updateWorld(IsoWorld.java:3336)
+zombie.iso.IsoWorld.updateInternal(IsoWorld.java:3428)
+zombie.iso.IsoWorld.update(IsoWorld.java:3361)
+zombie.gameStates.IngameState.updateInternal(IngameState.java:1505)
+zombie.gameStates.IngameState.update(IngameState.java:1325)
+zombie.gameStates.GameStateMachine.update(GameStateMachine.java:65)
+zombie.GameWindow.logic(GameWindow.java:390)
+zombie.GameWindow.frameStep(GameWindow.java:790)
+zombie.GameWindow.mainThreadStep(GameWindow.java:567)
+zombie.MainThread.mainLoop(MainThread.java:69)
+java.base/java.lang.Thread.run(Unknown Source)</t>
+  </si>
+  <si>
+    <t>Antidepressants - dose already active (no dose at all)</t>
+  </si>
+  <si>
+    <t>Sleeping pills - dose still active if give antidepressant first</t>
+  </si>
+  <si>
+    <t>caffeine pills - сделать OTC</t>
+  </si>
+  <si>
+    <t>Добавить крафт пакетов с кровью</t>
+  </si>
+  <si>
+    <t>Добавить больше времени на то, чтобы кровь восстанавливалась</t>
+  </si>
+  <si>
+    <t>Добавить обильную потерю крови при ранению в шею(если выйдет, то scratch не считать)</t>
+  </si>
+  <si>
+    <t>после конца действия - stress 90%, head pain, 1</t>
+  </si>
+  <si>
+    <t>добавить Item_Epinephrine (restore health to 75%, restore stamina to 90%, 20% increased move speed, fatigue to 0, if health is above do not decrease it)</t>
+  </si>
+  <si>
+    <t>Если использовать когда у персонажа больше 20% общего здоровья, то 50% шанс инсульта и мгновенной смерти</t>
   </si>
 </sst>
 </file>
@@ -2199,162 +2304,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:M67"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A5698E-D7F9-417D-926B-EC214A1B994A}">
+  <dimension ref="B3:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="71" customWidth="1"/>
+    <col min="2" max="2" width="105.7109375" customWidth="1"/>
+    <col min="3" max="3" width="124.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
+      <c r="B3" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>1</v>
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>3</v>
+      <c r="C6" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>16</v>
+      <c r="B8" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="C10" s="15" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C12" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>6</v>
+      <c r="B17" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>9</v>
+      <c r="B18" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="M60" s="3"/>
-    </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="63" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="64" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="33" x14ac:dyDescent="0.25">
-      <c r="B65" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" ht="33" x14ac:dyDescent="0.25">
-      <c r="B66" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" ht="33" x14ac:dyDescent="0.25">
-      <c r="B67" s="4" t="s">
-        <v>32</v>
+      <c r="B21" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A4C555-5941-44D5-8766-80774E93DFFB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="89.28515625" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DFFC06-8A2D-4F1B-A609-E04AC1694A75}">
   <dimension ref="B3:Z42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2753,6 +2817,162 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B3:M67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="71" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D36" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B64" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B65" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B66" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="B67" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3715F01A-79F6-4956-8F11-0E2F67879F36}">
   <dimension ref="B3:U42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2932,7 +3152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2517986B-6F4C-42D0-BD39-2D6A74ACE8BD}">
   <dimension ref="B3:R35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3231,7 +3451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EED2F2-04B6-485E-917E-1A8DD36BA090}">
   <dimension ref="B3:I48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3425,7 +3645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D345CE2-5F04-48E0-AE34-8739DA490F25}">
   <dimension ref="B3:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3549,7 +3769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED16C1-7749-4CB3-928F-9E4FA94C1568}">
   <dimension ref="B2:AB61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3866,7 +4086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7944FC-5C7A-4B02-B021-398DF4A45490}">
   <dimension ref="A1:T27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4055,7 +4275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6582FB11-E4E7-44CC-B6AC-D03433973810}">
   <dimension ref="B2:V21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4242,16 +4462,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A4C555-5941-44D5-8766-80774E93DFFB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="89.28515625" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5B2376-A2E5-4CC8-B33F-1E6EED63E6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06252A09-E206-4A5F-94F8-5C679A00402A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="6525" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TODO" sheetId="12" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="276">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1190,110 +1190,6 @@
   </si>
   <si>
     <t>debugFoodPoisoning=false</t>
-  </si>
-  <si>
-    <t>Progression of diseaseses keep progressing when offline</t>
-  </si>
-  <si>
-    <t>Consolidation all problems</t>
-  </si>
-  <si>
-    <t>Consolidating items such as the antibiotic ointment and cough syrup will bug out and remove the itme, but it will return after relogging.</t>
-  </si>
-  <si>
-    <t>Not sure if it's a bug or just desync hence why I'm putting it here but in multiplayer both me and my friend have different illness whenever checking him. He has gastrointeritus where as I see he has dystery, I see an infected hand whereas he doesn't. Hard to tell what is actually to worry about.</t>
-  </si>
-  <si>
-    <t>hi I found bug I think... I playing in MP with my friend. We have a doctor. I have insomnia and I can't sleep if I don't take a sleep pills, but I take it and nothing happens but when the doctor forces to me to take it it works and I can see "active mediaction" but when I take those pills "active medication" shows nothing...</t>
-  </si>
-  <si>
-    <t>Vanilla meds not work?</t>
-  </si>
-  <si>
-    <t>What exactly happened: I'm not sure what's going on, but the painkillers aren't working for me. I take the pill, the dose is consumed, but there's no sign of any effect—neither on the panel interface, nor on the icons on the right, nor any pain relief
--What steps did you take: took the painkillers to relieve the pain; the pill bottle; took a pill
--MP or single-player: SP. Вот этот коммент с подозрением надо посмотреть, скорее всего там все ок</t>
-  </si>
-  <si>
-    <t>When tryingn to stitch friend in self hosted multiplayer, the mini game window that opens immediately disappears</t>
-  </si>
-  <si>
-    <t>Тоже проверить действительно ли так или просто дистанция большая</t>
-  </si>
-  <si>
-    <t>MP,
-Washing hands
-[10-08-26 00:10:57.325] ERROR: General f:570474 st:34,309,308 at KahluaThread.flushErrorMessage &gt; dumping Lua stack trace
------------------------------------------
-STACK TRACE
------------------------------------------
-Lua((MOD:Extensive Health Rework Evolved B42)).update(EHR_WashHands.lua:184).
-[10-08-26 00:10:57.325] ERROR: General f:570474 st:34,309,308&gt; Lua((MOD:Extensive Health Rework Evolved B42)).update&gt; Exception thrown
-java.lang.IllegalStateException: Forward Direction cannot be zero length vector. at IsoGameCharacter.setForwardDirection(IsoGameCharacter.java:2827).
-Stack trace:
-zombie.characters.IsoGameCharacter.setForwardDirection(IsoGameCharacter.java:2827)
-zombie.characters.IsoGameCharacter.setForwardDirection(IsoGameCharacter.java:2808)
-zombie.characters.IsoGameCharacter.faceThisObjectAlt(IsoGameCharacter.java:10609)
-java.base/jdk.internal.reflect.DirectMethodHandleAccessor.invoke(Unknown Source)
-java.base/java.lang.reflect.Method.invoke(Unknown Source)
-se.krka.kahlua.integration.expose.caller.MethodCaller.call(MethodCaller.java:58)
-se.krka.kahlua.integration.expose.LuaJavaInvoker.call(LuaJavaInvoker.java:194)
-se.krka.kahlua.integration.expose.LuaJavaInvoker.call(LuaJavaInvoker.java:184)
-se.krka.kahlua.vm.KahluaThread.callJava(KahluaThread.java:178)
-Lua((MOD:Extensive Health Rework Evolved B42)).update(EHR_WashHands.lua:184)
-se.krka.kahlua.vm.KahluaThread.luaMainloop(KahluaThread.java:795)
-se.krka.kahlua.vm.KahluaThread.call(KahluaThread.java:162)
-se.krka.kahlua.vm.KahluaThread.pcall(KahluaThread.java:1740)
-se.krka.kahlua.vm.KahluaThread.pcallvoid(KahluaThread.java:1584)
-se.krka.kahlua.integration.LuaCaller.pcallvoid(LuaCaller.java:35)
-zombie.characters.CharacterTimedActions.LuaTimedActionNew.update(LuaTimedActionNew.java:87)
-zombie.characters.IsoGameCharacter.updateInternal(IsoGameCharacter.java:9189)
-zombie.characters.IsoGameCharacter.update(IsoGameCharacter.java:8820)
-zombie.characters.IsoPlayer.updateInternal1(IsoPlayer.java:2206)
-zombie.characters.IsoPlayer.update(IsoPlayer.java:2184)
-zombie.MovingObjectUpdateSchedulerUpdateBucket.update(MovingObjectUpdateSchedulerUpdateBucket.java:58)
-zombie.MovingObjectUpdateScheduler.update(MovingObjectUpdateScheduler.java:150)
-zombie.iso.IsoCell.ProcessObjects(IsoCell.java:2662)
-zombie.iso.IsoCell.updateInternal(IsoCell.java:4905)
-zombie.iso.IsoCell.update(IsoCell.java:4862)
-zombie.iso.IsoWorld.updateWorld(IsoWorld.java:3336)
-zombie.iso.IsoWorld.updateInternal(IsoWorld.java:3428)
-zombie.iso.IsoWorld.update(IsoWorld.java:3361)
-zombie.gameStates.IngameState.updateInternal(IngameState.java:1505)
-zombie.gameStates.IngameState.update(IngameState.java:1325)
-zombie.gameStates.GameStateMachine.update(GameStateMachine.java:65)
-zombie.GameWindow.logic(GameWindow.java:390)
-zombie.GameWindow.frameStep(GameWindow.java:790)
-zombie.GameWindow.mainThreadStep(GameWindow.java:567)
-zombie.MainThread.mainLoop(MainThread.java:69)
-java.base/java.lang.Thread.run(Unknown Source)</t>
-  </si>
-  <si>
-    <t>Antidepressants - dose already active (no dose at all)</t>
-  </si>
-  <si>
-    <t>Sleeping pills - dose still active if give antidepressant first</t>
-  </si>
-  <si>
-    <t>caffeine pills - сделать OTC</t>
-  </si>
-  <si>
-    <t>Добавить крафт пакетов с кровью</t>
-  </si>
-  <si>
-    <t>Добавить больше времени на то, чтобы кровь восстанавливалась</t>
-  </si>
-  <si>
-    <t>Добавить обильную потерю крови при ранению в шею(если выйдет, то scratch не считать)</t>
-  </si>
-  <si>
-    <t>после конца действия - stress 90%, head pain, 1</t>
-  </si>
-  <si>
-    <t>добавить Item_Epinephrine (restore health to 75%, restore stamina to 90%, 20% increased move speed, fatigue to 0, if health is above do not decrease it)</t>
-  </si>
-  <si>
-    <t>Если использовать когда у персонажа больше 20% общего здоровья, то 50% шанс инсульта и мгновенной смерти</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1580,6 +1476,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2305,101 +2202,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A5698E-D7F9-417D-926B-EC214A1B994A}">
-  <dimension ref="B3:C27"/>
+  <dimension ref="B10:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="105.7109375" customWidth="1"/>
     <col min="3" max="3" width="124.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>277</v>
-      </c>
-      <c r="C4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="C10" s="15" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>283</v>
-      </c>
-      <c r="C12" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="15" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>289</v>
-      </c>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="15"/>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="15"/>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>293</v>
-      </c>
+      <c r="B23" s="38"/>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>294</v>
-      </c>
+      <c r="B24" s="38"/>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>292</v>
-      </c>
+      <c r="B25" s="38"/>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>290</v>
-      </c>
+      <c r="B26" s="38"/>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>291</v>
-      </c>
+      <c r="B27" s="38"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExtensiveHealthReworkB42/Stats.xlsx
+++ b/ExtensiveHealthReworkB42/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\Mods\PZ\Custom Mods\EHR\EHR\Extensive Health Rework B42\ExtensiveHealthReworkB42\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06252A09-E206-4A5F-94F8-5C679A00402A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9751CC3C-284F-4823-AF1E-682C8372FC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="33525" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TODO" sheetId="12" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="286">
   <si>
     <t>- Cause: Rotten food (70%), burned food (5%), stale food (10%)</t>
   </si>
@@ -1190,6 +1190,36 @@
   </si>
   <si>
     <t>debugFoodPoisoning=false</t>
+  </si>
+  <si>
+    <t>New Craft Recipes</t>
+  </si>
+  <si>
+    <t>Plastic Strips: Any plastic Item(like bottles, plastic trays, etc), Scissors or any knife. Result should give 2-5 strips depending on the item.</t>
+  </si>
+  <si>
+    <t>Homemade Syringe (Pack):5x Pen(any pen but not pencils, etc)(Consumed), File(not consumed), Razor(not consumed), Scissors or any knife(not consumed), Duct Tape or Adhasive tape(consumed some of it), Glue or Epoxy(consumed some of it), 5 any needle(consumed)</t>
+  </si>
+  <si>
+    <t>Проверить нормально ли спавнится новый Ephineprine Auto Injector</t>
+  </si>
+  <si>
+    <t>Homemade IV kit: Sterile Syringe (Pack) 3 units or Homemade Syringe (Pack) 3 unis, 2 rubber hose (Consumed), Razor(not consumed), Scissors or Knife (not consumed), Any plastic bottle(Consumed)</t>
+  </si>
+  <si>
+    <t>Prepare Homemade Blood Bag:  Baking Tray or Baking Pan(not consumed), 10 Plastic Strips(Consumed), rubber hose(consumed), Homemade Syringe (Pack) 1 unit or Sterile Syringe (Pack)1 unit, Scissors or knife (not consumed)</t>
+  </si>
+  <si>
+    <t>Все рецепты должны быть включены в флаеры и у HER Doctor, EHR Surgeon</t>
+  </si>
+  <si>
+    <t>Должны нормально работать при Administer Medicine</t>
+  </si>
+  <si>
+    <t>Homemade Empty Blood Bag: Prepare Empty Blood Bag,  placed in cooking enviroment (like stove, campfire, etc)</t>
+  </si>
+  <si>
+    <t>При Draw Blood в Homemade Empty Blood Bag должен заменятся на соответствующий тип крови уже существующих мешков</t>
   </si>
 </sst>
 </file>
@@ -1464,6 +1494,9 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1476,7 +1509,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2202,36 +2234,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A5698E-D7F9-417D-926B-EC214A1B994A}">
-  <dimension ref="B10:C28"/>
+  <dimension ref="B2:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="105.7109375" customWidth="1"/>
     <col min="3" max="3" width="124.140625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="34" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C10" s="15"/>
     </row>
+    <row r="11" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>279</v>
+      </c>
+    </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="15"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="38"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="38"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="38"/>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="38"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="38"/>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="38"/>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>285</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3010,20 +3074,20 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D5">
@@ -3032,18 +3096,18 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D6">
@@ -3052,18 +3116,18 @@
       <c r="E6" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
@@ -3072,18 +3136,18 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
@@ -3092,78 +3156,78 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="3"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F16" s="3"/>
@@ -3397,61 +3461,61 @@
       </c>
     </row>
     <row r="32" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="36" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="35"/>
+      <c r="B33" s="36"/>
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="35"/>
+      <c r="B34" s="36"/>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="35"/>
+      <c r="B35" s="36"/>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="35"/>
+      <c r="B36" s="36"/>
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="35"/>
+      <c r="B37" s="36"/>
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="35"/>
+      <c r="B38" s="36"/>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="35"/>
+      <c r="B39" s="36"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="35"/>
+      <c r="B40" s="36"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="35"/>
+      <c r="B41" s="36"/>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="C42" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
@@ -3487,33 +3551,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="37" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="36"/>
+      <c r="B4" s="37"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="36"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="36"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="15"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="36"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="15"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="36"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="36"/>
+      <c r="B9" s="37"/>
       <c r="C9" s="15"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -4167,120 +4231,120 @@
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="37"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="37"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E21" t="s">
